--- a/output/paket/04_BÜTÇE VE HAKEDİŞ/17Eylül2026_Gym_Maltepe_Kesif_Ozeti_BoQ.xlsx
+++ b/output/paket/04_BÜTÇE VE HAKEDİŞ/17Eylül2026_Gym_Maltepe_Kesif_Ozeti_BoQ.xlsx
@@ -976,7 +976,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Rev E</t>
+          <t>Rev F</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev E · 17 Eylül 2026 · Tutarlar KDV hariç TL</t>
+          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev F · 17 Eylül 2026 · Tutarlar KDV hariç TL</t>
         </is>
       </c>
     </row>
@@ -1629,10 +1629,10 @@
         <v/>
       </c>
       <c r="E15" s="17" t="n">
-        <v>514423</v>
+        <v>540728</v>
       </c>
       <c r="F15" s="17" t="n">
-        <v>866708</v>
+        <v>909501</v>
       </c>
       <c r="G15" s="18" t="n">
         <v>0.2</v>
@@ -1665,10 +1665,10 @@
         <v/>
       </c>
       <c r="E16" s="24" t="n">
-        <v>402580</v>
+        <v>412220</v>
       </c>
       <c r="F16" s="24" t="n">
-        <v>682600</v>
+        <v>698140</v>
       </c>
       <c r="G16" s="25" t="n">
         <v>0.2</v>
@@ -1913,7 +1913,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev E · 17 Eylül 2026 · KDV hariç TL · sarı hücreler teklif veren firma tarafından doldurulacaktır</t>
+          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev F · 17 Eylül 2026 · KDV hariç TL · sarı hücreler teklif veren firma tarafından doldurulacaktır</t>
         </is>
       </c>
     </row>
@@ -9245,7 +9245,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev E · KDV hariç TL · sarı hücre teklif verence doldurulur</t>
+          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev F · KDV hariç TL · sarı hücre teklif verence doldurulur</t>
         </is>
       </c>
     </row>
@@ -9409,7 +9409,7 @@
         </is>
       </c>
       <c r="D8" s="55" t="n">
-        <v>10.3</v>
+        <v>16.8</v>
       </c>
       <c r="E8" s="44" t="n"/>
       <c r="F8" s="46">
@@ -9417,10 +9417,10 @@
         <v/>
       </c>
       <c r="G8" s="56" t="n">
-        <v>13905</v>
+        <v>22680</v>
       </c>
       <c r="H8" s="56" t="n">
-        <v>22660</v>
+        <v>36960</v>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
@@ -9440,7 +9440,7 @@
         </is>
       </c>
       <c r="D9" s="59" t="n">
-        <v>9.1</v>
+        <v>10.5</v>
       </c>
       <c r="E9" s="44" t="n"/>
       <c r="F9" s="54">
@@ -9448,10 +9448,10 @@
         <v/>
       </c>
       <c r="G9" s="60" t="n">
-        <v>10465</v>
+        <v>12075</v>
       </c>
       <c r="H9" s="60" t="n">
-        <v>17290</v>
+        <v>19950</v>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
@@ -9471,7 +9471,7 @@
         </is>
       </c>
       <c r="D10" s="55" t="n">
-        <v>10.7</v>
+        <v>4.4</v>
       </c>
       <c r="E10" s="44" t="n"/>
       <c r="F10" s="46">
@@ -9479,10 +9479,10 @@
         <v/>
       </c>
       <c r="G10" s="56" t="n">
-        <v>6634</v>
+        <v>2728</v>
       </c>
       <c r="H10" s="56" t="n">
-        <v>11235</v>
+        <v>4620</v>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
@@ -9502,7 +9502,7 @@
         </is>
       </c>
       <c r="D11" s="59" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="E11" s="44" t="n"/>
       <c r="F11" s="54">
@@ -9510,10 +9510,10 @@
         <v/>
       </c>
       <c r="G11" s="60" t="n">
-        <v>1932</v>
+        <v>1260</v>
       </c>
       <c r="H11" s="60" t="n">
-        <v>3312</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
@@ -9533,7 +9533,7 @@
         </is>
       </c>
       <c r="D12" s="55" t="n">
-        <v>7.4</v>
+        <v>15</v>
       </c>
       <c r="E12" s="44" t="n"/>
       <c r="F12" s="46">
@@ -9541,10 +9541,10 @@
         <v/>
       </c>
       <c r="G12" s="56" t="n">
-        <v>3996</v>
+        <v>8100</v>
       </c>
       <c r="H12" s="56" t="n">
-        <v>6660</v>
+        <v>13500</v>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
@@ -9750,7 +9750,7 @@
         </is>
       </c>
       <c r="D19" s="59" t="n">
-        <v>25.2</v>
+        <v>35.5</v>
       </c>
       <c r="E19" s="44" t="n"/>
       <c r="F19" s="54">
@@ -9758,10 +9758,10 @@
         <v/>
       </c>
       <c r="G19" s="60" t="n">
-        <v>19656</v>
+        <v>27690</v>
       </c>
       <c r="H19" s="60" t="n">
-        <v>32760</v>
+        <v>46150</v>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1">
@@ -9781,7 +9781,7 @@
         </is>
       </c>
       <c r="D20" s="55" t="n">
-        <v>26.8</v>
+        <v>42.3</v>
       </c>
       <c r="E20" s="44" t="n"/>
       <c r="F20" s="46">
@@ -9789,10 +9789,10 @@
         <v/>
       </c>
       <c r="G20" s="56" t="n">
-        <v>8576</v>
+        <v>13536</v>
       </c>
       <c r="H20" s="56" t="n">
-        <v>14472</v>
+        <v>22842</v>
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
@@ -10392,7 +10392,7 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>Elektrikli ani su ısıtıcı 6 kW (blok başına)</t>
+          <t>Depolu elektrikli boyler 100 L / 3 kW, emaye kaplı, magnezyum anotlu (blok başına)</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
@@ -10409,10 +10409,10 @@
         <v/>
       </c>
       <c r="G40" s="56" t="n">
-        <v>19600</v>
+        <v>23000</v>
       </c>
       <c r="H40" s="56" t="n">
-        <v>34000</v>
+        <v>39000</v>
       </c>
     </row>
     <row r="41" ht="26" customHeight="1">
@@ -10506,7 +10506,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev E · KDV hariç TL · sarı hücre teklif verence doldurulur</t>
+          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev F · KDV hariç TL · sarı hücre teklif verence doldurulur</t>
         </is>
       </c>
     </row>
@@ -10670,7 +10670,7 @@
         </is>
       </c>
       <c r="D8" s="55" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E8" s="44" t="n"/>
       <c r="F8" s="46">
@@ -10678,10 +10678,10 @@
         <v/>
       </c>
       <c r="G8" s="56" t="n">
-        <v>13020</v>
+        <v>13640</v>
       </c>
       <c r="H8" s="56" t="n">
-        <v>22050</v>
+        <v>23100</v>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
@@ -10918,7 +10918,7 @@
         </is>
       </c>
       <c r="D16" s="55" t="n">
-        <v>172</v>
+        <v>42</v>
       </c>
       <c r="E16" s="44" t="n"/>
       <c r="F16" s="46">
@@ -10926,10 +10926,10 @@
         <v/>
       </c>
       <c r="G16" s="56" t="n">
-        <v>18920</v>
+        <v>4620</v>
       </c>
       <c r="H16" s="56" t="n">
-        <v>31820</v>
+        <v>7770</v>
       </c>
     </row>
     <row r="17" ht="26" customHeight="1">
@@ -11073,7 +11073,7 @@
         </is>
       </c>
       <c r="D21" s="59" t="n">
-        <v>193</v>
+        <v>391</v>
       </c>
       <c r="E21" s="44" t="n"/>
       <c r="F21" s="54">
@@ -11081,10 +11081,10 @@
         <v/>
       </c>
       <c r="G21" s="60" t="n">
-        <v>27020</v>
+        <v>54740</v>
       </c>
       <c r="H21" s="60" t="n">
-        <v>44390</v>
+        <v>89930</v>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
@@ -11126,7 +11126,7 @@
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Su ısıtıcı besleme hattı 3×6 mm² + 32 A kesici + 30 mA kaçak akım</t>
+          <t>Boyler besleme hattı 3×2,5 mm² + 20 A kesici + 30 mA kaçak akım</t>
         </is>
       </c>
       <c r="C23" s="51" t="inlineStr">
@@ -11143,10 +11143,10 @@
         <v/>
       </c>
       <c r="G23" s="60" t="n">
-        <v>12800</v>
+        <v>8400</v>
       </c>
       <c r="H23" s="60" t="n">
-        <v>21600</v>
+        <v>14600</v>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
@@ -11737,7 +11737,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev E · 17 Eylül 2026 · Boşluklar MİNHA olarak (−) satırla düşülmüştür. Ölçüler mimari uygulama projesinden türetilmiştir.</t>
+          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev F · 17 Eylül 2026 · Boşluklar MİNHA olarak (−) satırla düşülmüştür. Ölçüler mimari uygulama projesinden türetilmiştir.</t>
         </is>
       </c>
     </row>

--- a/output/paket/04_BÜTÇE VE HAKEDİŞ/17Eylül2026_Gym_Maltepe_Kesif_Ozeti_BoQ.xlsx
+++ b/output/paket/04_BÜTÇE VE HAKEDİŞ/17Eylül2026_Gym_Maltepe_Kesif_Ozeti_BoQ.xlsx
@@ -976,7 +976,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Rev F</t>
+          <t>Rev G</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev F · 17 Eylül 2026 · Tutarlar KDV hariç TL</t>
+          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev G · 17 Eylül 2026 · Tutarlar KDV hariç TL</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev F · 17 Eylül 2026 · KDV hariç TL · sarı hücreler teklif veren firma tarafından doldurulacaktır</t>
+          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev G · 17 Eylül 2026 · KDV hariç TL · sarı hücreler teklif veren firma tarafından doldurulacaktır</t>
         </is>
       </c>
     </row>
@@ -9245,7 +9245,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev F · KDV hariç TL · sarı hücre teklif verence doldurulur</t>
+          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev G · KDV hariç TL · sarı hücre teklif verence doldurulur</t>
         </is>
       </c>
     </row>
@@ -10506,7 +10506,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev F · KDV hariç TL · sarı hücre teklif verence doldurulur</t>
+          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev G · KDV hariç TL · sarı hücre teklif verence doldurulur</t>
         </is>
       </c>
     </row>
@@ -11737,7 +11737,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev F · 17 Eylül 2026 · Boşluklar MİNHA olarak (−) satırla düşülmüştür. Ölçüler mimari uygulama projesinden türetilmiştir.</t>
+          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev G · 17 Eylül 2026 · Boşluklar MİNHA olarak (−) satırla düşülmüştür. Ölçüler mimari uygulama projesinden türetilmiştir.</t>
         </is>
       </c>
     </row>

--- a/output/paket/04_BÜTÇE VE HAKEDİŞ/17Eylül2026_Gym_Maltepe_Kesif_Ozeti_BoQ.xlsx
+++ b/output/paket/04_BÜTÇE VE HAKEDİŞ/17Eylül2026_Gym_Maltepe_Kesif_Ozeti_BoQ.xlsx
@@ -976,7 +976,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Rev G</t>
+          <t>Rev H</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev G · 17 Eylül 2026 · Tutarlar KDV hariç TL</t>
+          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev H · 17 Eylül 2026 · Tutarlar KDV hariç TL</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev G · 17 Eylül 2026 · KDV hariç TL · sarı hücreler teklif veren firma tarafından doldurulacaktır</t>
+          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev H · 17 Eylül 2026 · KDV hariç TL · sarı hücreler teklif veren firma tarafından doldurulacaktır</t>
         </is>
       </c>
     </row>
@@ -9245,7 +9245,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev G · KDV hariç TL · sarı hücre teklif verence doldurulur</t>
+          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev H · KDV hariç TL · sarı hücre teklif verence doldurulur</t>
         </is>
       </c>
     </row>
@@ -10506,7 +10506,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev G · KDV hariç TL · sarı hücre teklif verence doldurulur</t>
+          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev H · KDV hariç TL · sarı hücre teklif verence doldurulur</t>
         </is>
       </c>
     </row>
@@ -11737,7 +11737,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev G · 17 Eylül 2026 · Boşluklar MİNHA olarak (−) satırla düşülmüştür. Ölçüler mimari uygulama projesinden türetilmiştir.</t>
+          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev H · 17 Eylül 2026 · Boşluklar MİNHA olarak (−) satırla düşülmüştür. Ölçüler mimari uygulama projesinden türetilmiştir.</t>
         </is>
       </c>
     </row>

--- a/output/paket/04_BÜTÇE VE HAKEDİŞ/17Eylül2026_Gym_Maltepe_Kesif_Ozeti_BoQ.xlsx
+++ b/output/paket/04_BÜTÇE VE HAKEDİŞ/17Eylül2026_Gym_Maltepe_Kesif_Ozeti_BoQ.xlsx
@@ -1269,10 +1269,10 @@
         <v/>
       </c>
       <c r="E5" s="17" t="n">
-        <v>155793.6</v>
+        <v>155583.6</v>
       </c>
       <c r="F5" s="17" t="n">
-        <v>247875.9</v>
+        <v>247578.4</v>
       </c>
       <c r="G5" s="18" t="n">
         <v>0.2</v>
@@ -1305,10 +1305,10 @@
         <v/>
       </c>
       <c r="E6" s="24" t="n">
-        <v>354543</v>
+        <v>347975.5</v>
       </c>
       <c r="F6" s="24" t="n">
-        <v>450588</v>
+        <v>442263</v>
       </c>
       <c r="G6" s="25" t="n">
         <v>0.2</v>
@@ -1341,10 +1341,10 @@
         <v/>
       </c>
       <c r="E7" s="17" t="n">
-        <v>86050.2</v>
+        <v>85689.8</v>
       </c>
       <c r="F7" s="17" t="n">
-        <v>122188.4</v>
+        <v>121691.9</v>
       </c>
       <c r="G7" s="18" t="n">
         <v>0.2</v>
@@ -1377,10 +1377,10 @@
         <v/>
       </c>
       <c r="E8" s="24" t="n">
-        <v>254653.3</v>
+        <v>260315.7</v>
       </c>
       <c r="F8" s="24" t="n">
-        <v>377584.9</v>
+        <v>386457.8</v>
       </c>
       <c r="G8" s="25" t="n">
         <v>0.2</v>
@@ -1413,10 +1413,10 @@
         <v/>
       </c>
       <c r="E9" s="17" t="n">
-        <v>102628.85</v>
+        <v>99652.75</v>
       </c>
       <c r="F9" s="17" t="n">
-        <v>152964.3</v>
+        <v>148560.3</v>
       </c>
       <c r="G9" s="18" t="n">
         <v>0.2</v>
@@ -1449,10 +1449,10 @@
         <v/>
       </c>
       <c r="E10" s="24" t="n">
-        <v>309828.75</v>
+        <v>328250.65</v>
       </c>
       <c r="F10" s="24" t="n">
-        <v>466314.9</v>
+        <v>495717.6</v>
       </c>
       <c r="G10" s="25" t="n">
         <v>0.2</v>
@@ -1629,10 +1629,10 @@
         <v/>
       </c>
       <c r="E15" s="17" t="n">
-        <v>540728</v>
+        <v>539693</v>
       </c>
       <c r="F15" s="17" t="n">
-        <v>909501</v>
+        <v>907712</v>
       </c>
       <c r="G15" s="18" t="n">
         <v>0.2</v>
@@ -1665,10 +1665,10 @@
         <v/>
       </c>
       <c r="E16" s="24" t="n">
-        <v>412220</v>
+        <v>412340</v>
       </c>
       <c r="F16" s="24" t="n">
-        <v>698140</v>
+        <v>698350</v>
       </c>
       <c r="G16" s="25" t="n">
         <v>0.2</v>
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="G8" s="43" t="n">
-        <v>6.19</v>
+        <v>5.84</v>
       </c>
       <c r="H8" s="44" t="n"/>
       <c r="I8" s="45">
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="G14" s="43" t="n">
-        <v>60.42</v>
+        <v>58.57</v>
       </c>
       <c r="H14" s="44" t="n"/>
       <c r="I14" s="45">
@@ -2696,7 +2696,7 @@
         </is>
       </c>
       <c r="G17" s="52" t="n">
-        <v>31.76</v>
+        <v>31.94</v>
       </c>
       <c r="H17" s="44" t="n"/>
       <c r="I17" s="53">
@@ -2759,7 +2759,7 @@
         </is>
       </c>
       <c r="G18" s="43" t="n">
-        <v>22.31</v>
+        <v>22.34</v>
       </c>
       <c r="H18" s="44" t="n"/>
       <c r="I18" s="45">
@@ -2822,7 +2822,7 @@
         </is>
       </c>
       <c r="G19" s="52" t="n">
-        <v>32.98</v>
+        <v>32.77</v>
       </c>
       <c r="H19" s="44" t="n"/>
       <c r="I19" s="53">
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="G20" s="43" t="n">
-        <v>10.07</v>
+        <v>10.21</v>
       </c>
       <c r="H20" s="44" t="n"/>
       <c r="I20" s="45">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="G21" s="52" t="n">
-        <v>6.19</v>
+        <v>5.84</v>
       </c>
       <c r="H21" s="44" t="n"/>
       <c r="I21" s="53">
@@ -3038,7 +3038,7 @@
         </is>
       </c>
       <c r="G23" s="52" t="n">
-        <v>31.76</v>
+        <v>31.94</v>
       </c>
       <c r="H23" s="44" t="n"/>
       <c r="I23" s="53">
@@ -3101,7 +3101,7 @@
         </is>
       </c>
       <c r="G24" s="43" t="n">
-        <v>22.31</v>
+        <v>22.34</v>
       </c>
       <c r="H24" s="44" t="n"/>
       <c r="I24" s="45">
@@ -3164,7 +3164,7 @@
         </is>
       </c>
       <c r="G25" s="52" t="n">
-        <v>32.98</v>
+        <v>32.77</v>
       </c>
       <c r="H25" s="44" t="n"/>
       <c r="I25" s="53">
@@ -3227,7 +3227,7 @@
         </is>
       </c>
       <c r="G26" s="43" t="n">
-        <v>6.19</v>
+        <v>5.84</v>
       </c>
       <c r="H26" s="44" t="n"/>
       <c r="I26" s="45">
@@ -3290,7 +3290,7 @@
         </is>
       </c>
       <c r="G27" s="52" t="n">
-        <v>10.07</v>
+        <v>10.21</v>
       </c>
       <c r="H27" s="44" t="n"/>
       <c r="I27" s="53">
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="G28" s="43" t="n">
-        <v>31.76</v>
+        <v>31.94</v>
       </c>
       <c r="H28" s="44" t="n"/>
       <c r="I28" s="45">
@@ -3416,7 +3416,7 @@
         </is>
       </c>
       <c r="G29" s="52" t="n">
-        <v>40.62</v>
+        <v>55.41</v>
       </c>
       <c r="H29" s="44" t="n"/>
       <c r="I29" s="53">
@@ -3479,7 +3479,7 @@
         </is>
       </c>
       <c r="G30" s="43" t="n">
-        <v>23.65</v>
+        <v>24.39</v>
       </c>
       <c r="H30" s="44" t="n"/>
       <c r="I30" s="45">
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="G31" s="52" t="n">
-        <v>16.17</v>
+        <v>16.52</v>
       </c>
       <c r="H31" s="44" t="n"/>
       <c r="I31" s="53">
@@ -3632,7 +3632,7 @@
         </is>
       </c>
       <c r="G33" s="52" t="n">
-        <v>21.68</v>
+        <v>21.08</v>
       </c>
       <c r="H33" s="44" t="n"/>
       <c r="I33" s="53">
@@ -3695,7 +3695,7 @@
         </is>
       </c>
       <c r="G34" s="43" t="n">
-        <v>14.46</v>
+        <v>13.94</v>
       </c>
       <c r="H34" s="44" t="n"/>
       <c r="I34" s="45">
@@ -3758,7 +3758,7 @@
         </is>
       </c>
       <c r="G35" s="52" t="n">
-        <v>6.19</v>
+        <v>5.84</v>
       </c>
       <c r="H35" s="44" t="n"/>
       <c r="I35" s="53">
@@ -3821,7 +3821,7 @@
         </is>
       </c>
       <c r="G36" s="43" t="n">
-        <v>23.47</v>
+        <v>22.87</v>
       </c>
       <c r="H36" s="44" t="n"/>
       <c r="I36" s="45">
@@ -3884,7 +3884,7 @@
         </is>
       </c>
       <c r="G37" s="52" t="n">
-        <v>52.61</v>
+        <v>52.03</v>
       </c>
       <c r="H37" s="44" t="n"/>
       <c r="I37" s="53">
@@ -3974,7 +3974,7 @@
         </is>
       </c>
       <c r="G39" s="52" t="n">
-        <v>32.98</v>
+        <v>32.77</v>
       </c>
       <c r="H39" s="44" t="n"/>
       <c r="I39" s="53">
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="G40" s="43" t="n">
-        <v>10.07</v>
+        <v>10.21</v>
       </c>
       <c r="H40" s="44" t="n"/>
       <c r="I40" s="45">
@@ -4100,7 +4100,7 @@
         </is>
       </c>
       <c r="G41" s="52" t="n">
-        <v>6.19</v>
+        <v>5.84</v>
       </c>
       <c r="H41" s="44" t="n"/>
       <c r="I41" s="53">
@@ -4163,7 +4163,7 @@
         </is>
       </c>
       <c r="G42" s="43" t="n">
-        <v>54.07</v>
+        <v>54.28</v>
       </c>
       <c r="H42" s="44" t="n"/>
       <c r="I42" s="45">
@@ -4352,7 +4352,7 @@
         </is>
       </c>
       <c r="G45" s="52" t="n">
-        <v>286.08</v>
+        <v>336.35</v>
       </c>
       <c r="H45" s="44" t="n"/>
       <c r="I45" s="53">
@@ -4415,7 +4415,7 @@
         </is>
       </c>
       <c r="G46" s="43" t="n">
-        <v>8.35</v>
+        <v>8.09</v>
       </c>
       <c r="H46" s="44" t="n"/>
       <c r="I46" s="45">
@@ -4478,7 +4478,7 @@
         </is>
       </c>
       <c r="G47" s="52" t="n">
-        <v>43.05</v>
+        <v>42.98</v>
       </c>
       <c r="H47" s="44" t="n"/>
       <c r="I47" s="53">
@@ -6411,7 +6411,7 @@
         </is>
       </c>
       <c r="D8" s="55" t="n">
-        <v>6.19</v>
+        <v>5.84</v>
       </c>
       <c r="E8" s="56" t="n">
         <v>0</v>
@@ -6652,7 +6652,7 @@
         </is>
       </c>
       <c r="D14" s="55" t="n">
-        <v>60.42</v>
+        <v>58.57</v>
       </c>
       <c r="E14" s="56" t="n">
         <v>2250</v>
@@ -6761,7 +6761,7 @@
         </is>
       </c>
       <c r="D17" s="59" t="n">
-        <v>31.76</v>
+        <v>31.94</v>
       </c>
       <c r="E17" s="60" t="n">
         <v>320</v>
@@ -6805,7 +6805,7 @@
         </is>
       </c>
       <c r="D18" s="55" t="n">
-        <v>22.31</v>
+        <v>22.34</v>
       </c>
       <c r="E18" s="56" t="n">
         <v>420</v>
@@ -6849,7 +6849,7 @@
         </is>
       </c>
       <c r="D19" s="59" t="n">
-        <v>32.98</v>
+        <v>32.77</v>
       </c>
       <c r="E19" s="60" t="n">
         <v>520</v>
@@ -6893,7 +6893,7 @@
         </is>
       </c>
       <c r="D20" s="55" t="n">
-        <v>10.07</v>
+        <v>10.21</v>
       </c>
       <c r="E20" s="56" t="n">
         <v>480</v>
@@ -6937,7 +6937,7 @@
         </is>
       </c>
       <c r="D21" s="59" t="n">
-        <v>6.19</v>
+        <v>5.84</v>
       </c>
       <c r="E21" s="60" t="n">
         <v>560</v>
@@ -7002,7 +7002,7 @@
         </is>
       </c>
       <c r="D23" s="59" t="n">
-        <v>31.76</v>
+        <v>31.94</v>
       </c>
       <c r="E23" s="60" t="n">
         <v>2400</v>
@@ -7046,7 +7046,7 @@
         </is>
       </c>
       <c r="D24" s="55" t="n">
-        <v>22.31</v>
+        <v>22.34</v>
       </c>
       <c r="E24" s="56" t="n">
         <v>1350</v>
@@ -7090,7 +7090,7 @@
         </is>
       </c>
       <c r="D25" s="59" t="n">
-        <v>32.98</v>
+        <v>32.77</v>
       </c>
       <c r="E25" s="60" t="n">
         <v>950</v>
@@ -7134,7 +7134,7 @@
         </is>
       </c>
       <c r="D26" s="55" t="n">
-        <v>6.19</v>
+        <v>5.84</v>
       </c>
       <c r="E26" s="56" t="n">
         <v>750</v>
@@ -7178,7 +7178,7 @@
         </is>
       </c>
       <c r="D27" s="59" t="n">
-        <v>10.07</v>
+        <v>10.21</v>
       </c>
       <c r="E27" s="60" t="n">
         <v>850</v>
@@ -7222,7 +7222,7 @@
         </is>
       </c>
       <c r="D28" s="55" t="n">
-        <v>31.76</v>
+        <v>31.94</v>
       </c>
       <c r="E28" s="56" t="n">
         <v>650</v>
@@ -7266,7 +7266,7 @@
         </is>
       </c>
       <c r="D29" s="59" t="n">
-        <v>40.62</v>
+        <v>55.41</v>
       </c>
       <c r="E29" s="60" t="n">
         <v>210</v>
@@ -7310,7 +7310,7 @@
         </is>
       </c>
       <c r="D30" s="55" t="n">
-        <v>23.65</v>
+        <v>24.39</v>
       </c>
       <c r="E30" s="56" t="n">
         <v>240</v>
@@ -7354,7 +7354,7 @@
         </is>
       </c>
       <c r="D31" s="59" t="n">
-        <v>16.17</v>
+        <v>16.52</v>
       </c>
       <c r="E31" s="60" t="n">
         <v>180</v>
@@ -7419,7 +7419,7 @@
         </is>
       </c>
       <c r="D33" s="59" t="n">
-        <v>21.68</v>
+        <v>21.08</v>
       </c>
       <c r="E33" s="60" t="n">
         <v>780</v>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="D34" s="55" t="n">
-        <v>14.46</v>
+        <v>13.94</v>
       </c>
       <c r="E34" s="56" t="n">
         <v>780</v>
@@ -7507,7 +7507,7 @@
         </is>
       </c>
       <c r="D35" s="59" t="n">
-        <v>6.19</v>
+        <v>5.84</v>
       </c>
       <c r="E35" s="60" t="n">
         <v>480</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="D36" s="55" t="n">
-        <v>23.47</v>
+        <v>22.87</v>
       </c>
       <c r="E36" s="56" t="n">
         <v>480</v>
@@ -7595,7 +7595,7 @@
         </is>
       </c>
       <c r="D37" s="59" t="n">
-        <v>52.61</v>
+        <v>52.03</v>
       </c>
       <c r="E37" s="60" t="n">
         <v>95</v>
@@ -7660,7 +7660,7 @@
         </is>
       </c>
       <c r="D39" s="59" t="n">
-        <v>32.98</v>
+        <v>32.77</v>
       </c>
       <c r="E39" s="60" t="n">
         <v>1050</v>
@@ -7704,7 +7704,7 @@
         </is>
       </c>
       <c r="D40" s="55" t="n">
-        <v>10.07</v>
+        <v>10.21</v>
       </c>
       <c r="E40" s="56" t="n">
         <v>1050</v>
@@ -7748,7 +7748,7 @@
         </is>
       </c>
       <c r="D41" s="59" t="n">
-        <v>6.19</v>
+        <v>5.84</v>
       </c>
       <c r="E41" s="60" t="n">
         <v>1250</v>
@@ -7792,7 +7792,7 @@
         </is>
       </c>
       <c r="D42" s="55" t="n">
-        <v>54.07</v>
+        <v>54.28</v>
       </c>
       <c r="E42" s="56" t="n">
         <v>180</v>
@@ -7924,7 +7924,7 @@
         </is>
       </c>
       <c r="D45" s="59" t="n">
-        <v>286.08</v>
+        <v>336.35</v>
       </c>
       <c r="E45" s="60" t="n">
         <v>145</v>
@@ -7968,7 +7968,7 @@
         </is>
       </c>
       <c r="D46" s="55" t="n">
-        <v>8.35</v>
+        <v>8.09</v>
       </c>
       <c r="E46" s="56" t="n">
         <v>180</v>
@@ -8012,7 +8012,7 @@
         </is>
       </c>
       <c r="D47" s="59" t="n">
-        <v>43.05</v>
+        <v>42.98</v>
       </c>
       <c r="E47" s="60" t="n">
         <v>145</v>
@@ -9440,7 +9440,7 @@
         </is>
       </c>
       <c r="D9" s="59" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="E9" s="44" t="n"/>
       <c r="F9" s="54">
@@ -9448,10 +9448,10 @@
         <v/>
       </c>
       <c r="G9" s="60" t="n">
-        <v>12075</v>
+        <v>12190</v>
       </c>
       <c r="H9" s="60" t="n">
-        <v>19950</v>
+        <v>20140</v>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
@@ -9471,7 +9471,7 @@
         </is>
       </c>
       <c r="D10" s="55" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="E10" s="44" t="n"/>
       <c r="F10" s="46">
@@ -9479,10 +9479,10 @@
         <v/>
       </c>
       <c r="G10" s="56" t="n">
-        <v>2728</v>
+        <v>3162</v>
       </c>
       <c r="H10" s="56" t="n">
-        <v>4620</v>
+        <v>5355</v>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
@@ -9502,7 +9502,7 @@
         </is>
       </c>
       <c r="D11" s="59" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="E11" s="44" t="n"/>
       <c r="F11" s="54">
@@ -9510,10 +9510,10 @@
         <v/>
       </c>
       <c r="G11" s="60" t="n">
-        <v>1260</v>
+        <v>1050</v>
       </c>
       <c r="H11" s="60" t="n">
-        <v>2160</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
@@ -9533,7 +9533,7 @@
         </is>
       </c>
       <c r="D12" s="55" t="n">
-        <v>15</v>
+        <v>16.7</v>
       </c>
       <c r="E12" s="44" t="n"/>
       <c r="F12" s="46">
@@ -9541,10 +9541,10 @@
         <v/>
       </c>
       <c r="G12" s="56" t="n">
-        <v>8100</v>
+        <v>9018</v>
       </c>
       <c r="H12" s="56" t="n">
-        <v>13500</v>
+        <v>15030</v>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
@@ -9750,7 +9750,7 @@
         </is>
       </c>
       <c r="D19" s="59" t="n">
-        <v>35.5</v>
+        <v>35.6</v>
       </c>
       <c r="E19" s="44" t="n"/>
       <c r="F19" s="54">
@@ -9758,10 +9758,10 @@
         <v/>
       </c>
       <c r="G19" s="60" t="n">
-        <v>27690</v>
+        <v>27768</v>
       </c>
       <c r="H19" s="60" t="n">
-        <v>46150</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1">
@@ -9781,7 +9781,7 @@
         </is>
       </c>
       <c r="D20" s="55" t="n">
-        <v>42.3</v>
+        <v>44.1</v>
       </c>
       <c r="E20" s="44" t="n"/>
       <c r="F20" s="46">
@@ -9789,10 +9789,10 @@
         <v/>
       </c>
       <c r="G20" s="56" t="n">
-        <v>13536</v>
+        <v>14112</v>
       </c>
       <c r="H20" s="56" t="n">
-        <v>22842</v>
+        <v>23814</v>
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
@@ -9967,7 +9967,7 @@
         </is>
       </c>
       <c r="D26" s="55" t="n">
-        <v>35.8</v>
+        <v>34</v>
       </c>
       <c r="E26" s="44" t="n"/>
       <c r="F26" s="46">
@@ -9975,10 +9975,10 @@
         <v/>
       </c>
       <c r="G26" s="56" t="n">
-        <v>39380</v>
+        <v>37400</v>
       </c>
       <c r="H26" s="56" t="n">
-        <v>66230</v>
+        <v>62900</v>
       </c>
     </row>
     <row r="27" ht="26" customHeight="1">
@@ -10029,7 +10029,7 @@
         </is>
       </c>
       <c r="D28" s="55" t="n">
-        <v>34.2</v>
+        <v>31.9</v>
       </c>
       <c r="E28" s="44" t="n"/>
       <c r="F28" s="46">
@@ -10037,10 +10037,10 @@
         <v/>
       </c>
       <c r="G28" s="56" t="n">
-        <v>14364</v>
+        <v>13398</v>
       </c>
       <c r="H28" s="56" t="n">
-        <v>24624</v>
+        <v>22968</v>
       </c>
     </row>
     <row r="29" ht="26" customHeight="1">
@@ -11538,7 +11538,7 @@
         </is>
       </c>
       <c r="D36" s="55" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E36" s="44" t="n"/>
       <c r="F36" s="46">
@@ -11546,10 +11546,10 @@
         <v/>
       </c>
       <c r="G36" s="56" t="n">
-        <v>12600</v>
+        <v>12720</v>
       </c>
       <c r="H36" s="56" t="n">
-        <v>22050</v>
+        <v>22260</v>
       </c>
     </row>
     <row r="37" ht="26" customHeight="1">
@@ -11848,7 +11848,7 @@
       <c r="F7" s="55" t="n"/>
       <c r="G7" s="55" t="n"/>
       <c r="H7" s="70" t="n">
-        <v>15.65</v>
+        <v>15.44</v>
       </c>
       <c r="I7" s="71" t="n"/>
     </row>
@@ -11873,7 +11873,7 @@
       <c r="F8" s="59" t="n"/>
       <c r="G8" s="59" t="n"/>
       <c r="H8" s="73" t="n">
-        <v>31.76</v>
+        <v>31.94</v>
       </c>
       <c r="I8" s="74" t="n"/>
     </row>
@@ -11898,7 +11898,7 @@
       <c r="F9" s="55" t="n"/>
       <c r="G9" s="55" t="n"/>
       <c r="H9" s="70" t="n">
-        <v>22.31</v>
+        <v>22.34</v>
       </c>
       <c r="I9" s="71" t="n"/>
     </row>
@@ -11948,7 +11948,7 @@
       <c r="F11" s="55" t="n"/>
       <c r="G11" s="55" t="n"/>
       <c r="H11" s="70" t="n">
-        <v>4.48</v>
+        <v>4.53</v>
       </c>
       <c r="I11" s="71" t="n"/>
     </row>
@@ -11973,7 +11973,7 @@
       <c r="F12" s="59" t="n"/>
       <c r="G12" s="59" t="n"/>
       <c r="H12" s="73" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="I12" s="74" t="n"/>
     </row>
@@ -11998,7 +11998,7 @@
       <c r="F13" s="55" t="n"/>
       <c r="G13" s="55" t="n"/>
       <c r="H13" s="70" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="I13" s="71" t="n"/>
     </row>
@@ -12023,7 +12023,7 @@
       <c r="F14" s="59" t="n"/>
       <c r="G14" s="59" t="n"/>
       <c r="H14" s="73" t="n">
-        <v>5.59</v>
+        <v>5.68</v>
       </c>
       <c r="I14" s="74" t="n"/>
     </row>
@@ -12048,7 +12048,7 @@
       <c r="F15" s="55" t="n"/>
       <c r="G15" s="55" t="n"/>
       <c r="H15" s="70" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="I15" s="71" t="n"/>
     </row>
@@ -12073,7 +12073,7 @@
       <c r="F16" s="59" t="n"/>
       <c r="G16" s="59" t="n"/>
       <c r="H16" s="73" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="I16" s="74" t="n"/>
     </row>
@@ -12098,7 +12098,7 @@
       <c r="F17" s="55" t="n"/>
       <c r="G17" s="55" t="n"/>
       <c r="H17" s="70" t="n">
-        <v>0.47</v>
+        <v>0.68</v>
       </c>
       <c r="I17" s="71" t="n"/>
     </row>
@@ -12235,7 +12235,7 @@
       <c r="F24" s="55" t="n"/>
       <c r="G24" s="55" t="n"/>
       <c r="H24" s="70" t="n">
-        <v>15.65</v>
+        <v>15.44</v>
       </c>
       <c r="I24" s="71" t="n"/>
     </row>
@@ -12260,7 +12260,7 @@
       <c r="F25" s="59" t="n"/>
       <c r="G25" s="59" t="n"/>
       <c r="H25" s="73" t="n">
-        <v>31.76</v>
+        <v>31.94</v>
       </c>
       <c r="I25" s="74" t="n"/>
     </row>
@@ -12285,7 +12285,7 @@
       <c r="F26" s="55" t="n"/>
       <c r="G26" s="55" t="n"/>
       <c r="H26" s="70" t="n">
-        <v>22.31</v>
+        <v>22.34</v>
       </c>
       <c r="I26" s="71" t="n"/>
     </row>
@@ -12335,7 +12335,7 @@
       <c r="F28" s="55" t="n"/>
       <c r="G28" s="55" t="n"/>
       <c r="H28" s="70" t="n">
-        <v>4.48</v>
+        <v>4.53</v>
       </c>
       <c r="I28" s="71" t="n"/>
     </row>
@@ -12360,7 +12360,7 @@
       <c r="F29" s="59" t="n"/>
       <c r="G29" s="59" t="n"/>
       <c r="H29" s="73" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="I29" s="74" t="n"/>
     </row>
@@ -12385,7 +12385,7 @@
       <c r="F30" s="55" t="n"/>
       <c r="G30" s="55" t="n"/>
       <c r="H30" s="70" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="I30" s="71" t="n"/>
     </row>
@@ -12410,7 +12410,7 @@
       <c r="F31" s="59" t="n"/>
       <c r="G31" s="59" t="n"/>
       <c r="H31" s="73" t="n">
-        <v>5.59</v>
+        <v>5.68</v>
       </c>
       <c r="I31" s="74" t="n"/>
     </row>
@@ -12435,7 +12435,7 @@
       <c r="F32" s="55" t="n"/>
       <c r="G32" s="55" t="n"/>
       <c r="H32" s="70" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="I32" s="71" t="n"/>
     </row>
@@ -12460,7 +12460,7 @@
       <c r="F33" s="59" t="n"/>
       <c r="G33" s="59" t="n"/>
       <c r="H33" s="73" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="I33" s="74" t="n"/>
     </row>
@@ -12485,7 +12485,7 @@
       <c r="F34" s="55" t="n"/>
       <c r="G34" s="55" t="n"/>
       <c r="H34" s="70" t="n">
-        <v>0.47</v>
+        <v>0.68</v>
       </c>
       <c r="I34" s="71" t="n"/>
     </row>
@@ -12622,7 +12622,7 @@
       <c r="F41" s="55" t="n"/>
       <c r="G41" s="55" t="n"/>
       <c r="H41" s="70" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="I41" s="71" t="n"/>
     </row>
@@ -12647,7 +12647,7 @@
       <c r="F42" s="59" t="n"/>
       <c r="G42" s="59" t="n"/>
       <c r="H42" s="73" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="I42" s="74" t="n"/>
     </row>
@@ -12672,7 +12672,7 @@
       <c r="F43" s="55" t="n"/>
       <c r="G43" s="55" t="n"/>
       <c r="H43" s="70" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="I43" s="71" t="n"/>
     </row>
@@ -12697,7 +12697,7 @@
       <c r="F44" s="59" t="n"/>
       <c r="G44" s="59" t="n"/>
       <c r="H44" s="73" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="I44" s="74" t="n"/>
     </row>
@@ -13576,7 +13576,7 @@
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>Erkek duş bölme duvarı (çevre 5.41 m)</t>
+          <t>Erkek duş bölme duvarı (çevre 5.24 m)</t>
         </is>
       </c>
       <c r="C86" s="69" t="inlineStr">
@@ -13588,14 +13588,14 @@
         <v>1</v>
       </c>
       <c r="E86" s="55" t="n">
-        <v>5.41</v>
+        <v>5.24</v>
       </c>
       <c r="F86" s="55" t="n"/>
       <c r="G86" s="55" t="n">
         <v>3.2</v>
       </c>
       <c r="H86" s="70" t="n">
-        <v>17.312</v>
+        <v>16.768</v>
       </c>
       <c r="I86" s="71" t="n"/>
     </row>
@@ -13605,7 +13605,7 @@
       </c>
       <c r="B87" s="48" t="inlineStr">
         <is>
-          <t>Erkek WC bölme duvarı (çevre 5.4 m)</t>
+          <t>Erkek WC bölme duvarı (çevre 5.24 m)</t>
         </is>
       </c>
       <c r="C87" s="72" t="inlineStr">
@@ -13617,14 +13617,14 @@
         <v>1</v>
       </c>
       <c r="E87" s="59" t="n">
-        <v>5.4</v>
+        <v>5.24</v>
       </c>
       <c r="F87" s="59" t="n"/>
       <c r="G87" s="59" t="n">
         <v>3.2</v>
       </c>
       <c r="H87" s="73" t="n">
-        <v>17.28</v>
+        <v>16.768</v>
       </c>
       <c r="I87" s="74" t="n"/>
     </row>
@@ -13634,7 +13634,7 @@
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>Kadin duş bölme duvarı (çevre 4.76 m)</t>
+          <t>Kadin duş bölme duvarı (çevre 4.68 m)</t>
         </is>
       </c>
       <c r="C88" s="69" t="inlineStr">
@@ -13646,14 +13646,14 @@
         <v>1</v>
       </c>
       <c r="E88" s="55" t="n">
-        <v>4.76</v>
+        <v>4.68</v>
       </c>
       <c r="F88" s="55" t="n"/>
       <c r="G88" s="55" t="n">
         <v>3.2</v>
       </c>
       <c r="H88" s="70" t="n">
-        <v>15.232</v>
+        <v>14.976</v>
       </c>
       <c r="I88" s="71" t="n"/>
     </row>
@@ -13663,7 +13663,7 @@
       </c>
       <c r="B89" s="48" t="inlineStr">
         <is>
-          <t>Kadin WC bölme duvarı (çevre 5.04 m)</t>
+          <t>Kadin WC bölme duvarı (çevre 4.87 m)</t>
         </is>
       </c>
       <c r="C89" s="72" t="inlineStr">
@@ -13675,14 +13675,14 @@
         <v>1</v>
       </c>
       <c r="E89" s="59" t="n">
-        <v>5.04</v>
+        <v>4.87</v>
       </c>
       <c r="F89" s="59" t="n"/>
       <c r="G89" s="59" t="n">
         <v>3.2</v>
       </c>
       <c r="H89" s="73" t="n">
-        <v>16.128</v>
+        <v>15.584</v>
       </c>
       <c r="I89" s="74" t="n"/>
     </row>
@@ -14105,7 +14105,7 @@
       <c r="F108" s="55" t="n"/>
       <c r="G108" s="55" t="n"/>
       <c r="H108" s="70" t="n">
-        <v>31.76</v>
+        <v>31.94</v>
       </c>
       <c r="I108" s="71" t="n"/>
     </row>
@@ -14242,7 +14242,7 @@
       <c r="F115" s="55" t="n"/>
       <c r="G115" s="55" t="n"/>
       <c r="H115" s="70" t="n">
-        <v>22.31</v>
+        <v>22.34</v>
       </c>
       <c r="I115" s="71" t="n"/>
     </row>
@@ -14379,7 +14379,7 @@
       <c r="F122" s="55" t="n"/>
       <c r="G122" s="55" t="n"/>
       <c r="H122" s="70" t="n">
-        <v>15.65</v>
+        <v>15.44</v>
       </c>
       <c r="I122" s="71" t="n"/>
     </row>
@@ -14541,7 +14541,7 @@
       <c r="F130" s="55" t="n"/>
       <c r="G130" s="55" t="n"/>
       <c r="H130" s="70" t="n">
-        <v>4.48</v>
+        <v>4.53</v>
       </c>
       <c r="I130" s="71" t="n"/>
     </row>
@@ -14566,7 +14566,7 @@
       <c r="F131" s="59" t="n"/>
       <c r="G131" s="59" t="n"/>
       <c r="H131" s="73" t="n">
-        <v>5.59</v>
+        <v>5.68</v>
       </c>
       <c r="I131" s="74" t="n"/>
     </row>
@@ -14703,7 +14703,7 @@
       <c r="F138" s="55" t="n"/>
       <c r="G138" s="55" t="n"/>
       <c r="H138" s="70" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="I138" s="71" t="n"/>
     </row>
@@ -14728,7 +14728,7 @@
       <c r="F139" s="59" t="n"/>
       <c r="G139" s="59" t="n"/>
       <c r="H139" s="73" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="I139" s="74" t="n"/>
     </row>
@@ -14753,7 +14753,7 @@
       <c r="F140" s="55" t="n"/>
       <c r="G140" s="55" t="n"/>
       <c r="H140" s="70" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="I140" s="71" t="n"/>
     </row>
@@ -14778,7 +14778,7 @@
       <c r="F141" s="59" t="n"/>
       <c r="G141" s="59" t="n"/>
       <c r="H141" s="73" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="I141" s="74" t="n"/>
     </row>
@@ -14915,7 +14915,7 @@
       <c r="F148" s="55" t="n"/>
       <c r="G148" s="55" t="n"/>
       <c r="H148" s="70" t="n">
-        <v>31.76</v>
+        <v>31.94</v>
       </c>
       <c r="I148" s="71" t="n"/>
     </row>
@@ -15052,7 +15052,7 @@
       <c r="F155" s="55" t="n"/>
       <c r="G155" s="55" t="n"/>
       <c r="H155" s="70" t="n">
-        <v>22.31</v>
+        <v>22.34</v>
       </c>
       <c r="I155" s="71" t="n"/>
     </row>
@@ -15189,7 +15189,7 @@
       <c r="F162" s="55" t="n"/>
       <c r="G162" s="55" t="n"/>
       <c r="H162" s="70" t="n">
-        <v>15.65</v>
+        <v>15.44</v>
       </c>
       <c r="I162" s="71" t="n"/>
     </row>
@@ -15351,7 +15351,7 @@
       <c r="F170" s="55" t="n"/>
       <c r="G170" s="55" t="n"/>
       <c r="H170" s="70" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="I170" s="71" t="n"/>
     </row>
@@ -15376,7 +15376,7 @@
       <c r="F171" s="59" t="n"/>
       <c r="G171" s="59" t="n"/>
       <c r="H171" s="73" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="I171" s="74" t="n"/>
     </row>
@@ -15401,7 +15401,7 @@
       <c r="F172" s="55" t="n"/>
       <c r="G172" s="55" t="n"/>
       <c r="H172" s="70" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="I172" s="71" t="n"/>
     </row>
@@ -15426,7 +15426,7 @@
       <c r="F173" s="59" t="n"/>
       <c r="G173" s="59" t="n"/>
       <c r="H173" s="73" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="I173" s="74" t="n"/>
     </row>
@@ -15563,7 +15563,7 @@
       <c r="F180" s="55" t="n"/>
       <c r="G180" s="55" t="n"/>
       <c r="H180" s="70" t="n">
-        <v>4.48</v>
+        <v>4.53</v>
       </c>
       <c r="I180" s="71" t="n"/>
     </row>
@@ -15588,7 +15588,7 @@
       <c r="F181" s="59" t="n"/>
       <c r="G181" s="59" t="n"/>
       <c r="H181" s="73" t="n">
-        <v>5.59</v>
+        <v>5.68</v>
       </c>
       <c r="I181" s="74" t="n"/>
     </row>
@@ -15725,7 +15725,7 @@
       <c r="F188" s="55" t="n"/>
       <c r="G188" s="55" t="n"/>
       <c r="H188" s="70" t="n">
-        <v>31.76</v>
+        <v>31.94</v>
       </c>
       <c r="I188" s="71" t="n"/>
     </row>
@@ -15859,12 +15859,12 @@
         <v>1</v>
       </c>
       <c r="E195" s="55" t="n">
-        <v>22.59</v>
+        <v>22.62</v>
       </c>
       <c r="F195" s="55" t="n"/>
       <c r="G195" s="55" t="n"/>
       <c r="H195" s="70" t="n">
-        <v>22.59</v>
+        <v>22.62</v>
       </c>
       <c r="I195" s="71" t="n"/>
     </row>
@@ -15886,12 +15886,12 @@
         <v>1</v>
       </c>
       <c r="E196" s="59" t="n">
-        <v>30.63</v>
+        <v>45.39</v>
       </c>
       <c r="F196" s="59" t="n"/>
       <c r="G196" s="59" t="n"/>
       <c r="H196" s="73" t="n">
-        <v>30.63</v>
+        <v>45.39</v>
       </c>
       <c r="I196" s="74" t="n"/>
     </row>
@@ -16052,12 +16052,12 @@
         <v>1</v>
       </c>
       <c r="E204" s="55" t="n">
-        <v>20.48</v>
+        <v>21.12</v>
       </c>
       <c r="F204" s="55" t="n"/>
       <c r="G204" s="55" t="n"/>
       <c r="H204" s="70" t="n">
-        <v>20.48</v>
+        <v>21.12</v>
       </c>
       <c r="I204" s="71" t="n"/>
     </row>
@@ -16133,12 +16133,12 @@
         <v>1</v>
       </c>
       <c r="E207" s="59" t="n">
-        <v>18.07</v>
+        <v>18.17</v>
       </c>
       <c r="F207" s="59" t="n"/>
       <c r="G207" s="59" t="n"/>
       <c r="H207" s="73" t="n">
-        <v>18.07</v>
+        <v>18.17</v>
       </c>
       <c r="I207" s="74" t="n"/>
     </row>
@@ -16299,12 +16299,12 @@
         <v>1</v>
       </c>
       <c r="E215" s="55" t="n">
-        <v>8.470000000000001</v>
+        <v>8.52</v>
       </c>
       <c r="F215" s="55" t="n"/>
       <c r="G215" s="55" t="n"/>
       <c r="H215" s="70" t="n">
-        <v>8.470000000000001</v>
+        <v>8.52</v>
       </c>
       <c r="I215" s="71" t="n"/>
     </row>
@@ -16353,12 +16353,12 @@
         <v>1</v>
       </c>
       <c r="E217" s="55" t="n">
-        <v>9.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F217" s="55" t="n"/>
       <c r="G217" s="55" t="n"/>
       <c r="H217" s="70" t="n">
-        <v>9.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I217" s="71" t="n"/>
     </row>
@@ -16507,7 +16507,7 @@
       </c>
       <c r="B225" s="7" t="inlineStr">
         <is>
-          <t>Erkek duş — çevre 5.41 m × tavan kotu 2,40 m</t>
+          <t>Erkek duş — çevre 5.24 m × tavan kotu 2,40 m</t>
         </is>
       </c>
       <c r="C225" s="69" t="inlineStr">
@@ -16519,14 +16519,14 @@
         <v>1</v>
       </c>
       <c r="E225" s="55" t="n">
-        <v>5.41</v>
+        <v>5.24</v>
       </c>
       <c r="F225" s="55" t="n"/>
       <c r="G225" s="55" t="n">
         <v>2.4</v>
       </c>
       <c r="H225" s="70" t="n">
-        <v>12.984</v>
+        <v>12.576</v>
       </c>
       <c r="I225" s="71" t="n"/>
     </row>
@@ -16536,7 +16536,7 @@
       </c>
       <c r="B226" s="48" t="inlineStr">
         <is>
-          <t>Kadin duş — çevre 4.76 m × tavan kotu 2,40 m</t>
+          <t>Kadin duş — çevre 4.68 m × tavan kotu 2,40 m</t>
         </is>
       </c>
       <c r="C226" s="72" t="inlineStr">
@@ -16548,14 +16548,14 @@
         <v>1</v>
       </c>
       <c r="E226" s="59" t="n">
-        <v>4.76</v>
+        <v>4.68</v>
       </c>
       <c r="F226" s="59" t="n"/>
       <c r="G226" s="59" t="n">
         <v>2.4</v>
       </c>
       <c r="H226" s="73" t="n">
-        <v>11.424</v>
+        <v>11.232</v>
       </c>
       <c r="I226" s="74" t="n"/>
     </row>
@@ -16735,7 +16735,7 @@
       </c>
       <c r="B235" s="7" t="inlineStr">
         <is>
-          <t>Erkek WC — çevre 5.4 m × h 1,60 m</t>
+          <t>Erkek WC — çevre 5.24 m × h 1,60 m</t>
         </is>
       </c>
       <c r="C235" s="69" t="inlineStr">
@@ -16747,14 +16747,14 @@
         <v>1</v>
       </c>
       <c r="E235" s="55" t="n">
-        <v>5.4</v>
+        <v>5.24</v>
       </c>
       <c r="F235" s="55" t="n"/>
       <c r="G235" s="55" t="n">
         <v>1.6</v>
       </c>
       <c r="H235" s="70" t="n">
-        <v>8.640000000000001</v>
+        <v>8.384</v>
       </c>
       <c r="I235" s="71" t="n"/>
     </row>
@@ -16764,7 +16764,7 @@
       </c>
       <c r="B236" s="48" t="inlineStr">
         <is>
-          <t>Kadin WC — çevre 5.04 m × h 1,60 m</t>
+          <t>Kadin WC — çevre 4.87 m × h 1,60 m</t>
         </is>
       </c>
       <c r="C236" s="72" t="inlineStr">
@@ -16776,14 +16776,14 @@
         <v>1</v>
       </c>
       <c r="E236" s="59" t="n">
-        <v>5.04</v>
+        <v>4.87</v>
       </c>
       <c r="F236" s="59" t="n"/>
       <c r="G236" s="59" t="n">
         <v>1.6</v>
       </c>
       <c r="H236" s="73" t="n">
-        <v>8.064</v>
+        <v>7.792</v>
       </c>
       <c r="I236" s="74" t="n"/>
     </row>
@@ -16978,7 +16978,7 @@
       <c r="F245" s="55" t="n"/>
       <c r="G245" s="55" t="n"/>
       <c r="H245" s="70" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="I245" s="71" t="n"/>
     </row>
@@ -17003,7 +17003,7 @@
       <c r="F246" s="59" t="n"/>
       <c r="G246" s="59" t="n"/>
       <c r="H246" s="73" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="I246" s="74" t="n"/>
     </row>
@@ -17028,7 +17028,7 @@
       <c r="F247" s="55" t="n"/>
       <c r="G247" s="55" t="n"/>
       <c r="H247" s="70" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="I247" s="71" t="n"/>
     </row>
@@ -17053,7 +17053,7 @@
       <c r="F248" s="59" t="n"/>
       <c r="G248" s="59" t="n"/>
       <c r="H248" s="73" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="I248" s="74" t="n"/>
     </row>
@@ -17187,14 +17187,14 @@
         <v>1</v>
       </c>
       <c r="E255" s="55" t="n">
-        <v>5.41</v>
+        <v>5.24</v>
       </c>
       <c r="F255" s="55" t="n"/>
       <c r="G255" s="55" t="n">
         <v>2</v>
       </c>
       <c r="H255" s="70" t="n">
-        <v>10.82</v>
+        <v>10.48</v>
       </c>
       <c r="I255" s="71" t="n"/>
     </row>
@@ -17216,14 +17216,14 @@
         <v>1</v>
       </c>
       <c r="E256" s="59" t="n">
-        <v>5.4</v>
+        <v>5.24</v>
       </c>
       <c r="F256" s="59" t="n"/>
       <c r="G256" s="59" t="n">
         <v>0.3</v>
       </c>
       <c r="H256" s="73" t="n">
-        <v>1.62</v>
+        <v>1.572</v>
       </c>
       <c r="I256" s="74" t="n"/>
     </row>
@@ -17245,14 +17245,14 @@
         <v>1</v>
       </c>
       <c r="E257" s="55" t="n">
-        <v>4.76</v>
+        <v>4.68</v>
       </c>
       <c r="F257" s="55" t="n"/>
       <c r="G257" s="55" t="n">
         <v>2</v>
       </c>
       <c r="H257" s="70" t="n">
-        <v>9.52</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="I257" s="71" t="n"/>
     </row>
@@ -17274,14 +17274,14 @@
         <v>1</v>
       </c>
       <c r="E258" s="59" t="n">
-        <v>5.04</v>
+        <v>4.87</v>
       </c>
       <c r="F258" s="59" t="n"/>
       <c r="G258" s="59" t="n">
         <v>0.3</v>
       </c>
       <c r="H258" s="73" t="n">
-        <v>1.512</v>
+        <v>1.461</v>
       </c>
       <c r="I258" s="74" t="n"/>
     </row>
@@ -17415,12 +17415,12 @@
         <v>1</v>
       </c>
       <c r="E265" s="55" t="n">
-        <v>5.41</v>
+        <v>5.24</v>
       </c>
       <c r="F265" s="55" t="n"/>
       <c r="G265" s="55" t="n"/>
       <c r="H265" s="70" t="n">
-        <v>5.41</v>
+        <v>5.24</v>
       </c>
       <c r="I265" s="71" t="n"/>
     </row>
@@ -17442,12 +17442,12 @@
         <v>1</v>
       </c>
       <c r="E266" s="59" t="n">
-        <v>5.4</v>
+        <v>5.24</v>
       </c>
       <c r="F266" s="59" t="n"/>
       <c r="G266" s="59" t="n"/>
       <c r="H266" s="73" t="n">
-        <v>5.4</v>
+        <v>5.24</v>
       </c>
       <c r="I266" s="74" t="n"/>
     </row>
@@ -17469,12 +17469,12 @@
         <v>1</v>
       </c>
       <c r="E267" s="55" t="n">
-        <v>4.76</v>
+        <v>4.68</v>
       </c>
       <c r="F267" s="55" t="n"/>
       <c r="G267" s="55" t="n"/>
       <c r="H267" s="70" t="n">
-        <v>4.76</v>
+        <v>4.68</v>
       </c>
       <c r="I267" s="71" t="n"/>
     </row>
@@ -17496,12 +17496,12 @@
         <v>1</v>
       </c>
       <c r="E268" s="59" t="n">
-        <v>5.04</v>
+        <v>4.87</v>
       </c>
       <c r="F268" s="59" t="n"/>
       <c r="G268" s="59" t="n"/>
       <c r="H268" s="73" t="n">
-        <v>5.04</v>
+        <v>4.87</v>
       </c>
       <c r="I268" s="74" t="n"/>
     </row>
@@ -17665,7 +17665,7 @@
       <c r="F276" s="55" t="n"/>
       <c r="G276" s="55" t="n"/>
       <c r="H276" s="70" t="n">
-        <v>15.65</v>
+        <v>15.44</v>
       </c>
       <c r="I276" s="71" t="n"/>
     </row>
@@ -17827,7 +17827,7 @@
       <c r="F284" s="55" t="n"/>
       <c r="G284" s="55" t="n"/>
       <c r="H284" s="70" t="n">
-        <v>4.48</v>
+        <v>4.53</v>
       </c>
       <c r="I284" s="71" t="n"/>
     </row>
@@ -17852,7 +17852,7 @@
       <c r="F285" s="59" t="n"/>
       <c r="G285" s="59" t="n"/>
       <c r="H285" s="73" t="n">
-        <v>5.59</v>
+        <v>5.68</v>
       </c>
       <c r="I285" s="74" t="n"/>
     </row>
@@ -17989,7 +17989,7 @@
       <c r="F292" s="55" t="n"/>
       <c r="G292" s="55" t="n"/>
       <c r="H292" s="70" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="I292" s="71" t="n"/>
     </row>
@@ -18014,7 +18014,7 @@
       <c r="F293" s="59" t="n"/>
       <c r="G293" s="59" t="n"/>
       <c r="H293" s="73" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="I293" s="74" t="n"/>
     </row>
@@ -18039,7 +18039,7 @@
       <c r="F294" s="55" t="n"/>
       <c r="G294" s="55" t="n"/>
       <c r="H294" s="70" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="I294" s="71" t="n"/>
     </row>
@@ -18064,7 +18064,7 @@
       <c r="F295" s="59" t="n"/>
       <c r="G295" s="59" t="n"/>
       <c r="H295" s="73" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="I295" s="74" t="n"/>
     </row>
@@ -18201,7 +18201,7 @@
       <c r="F302" s="55" t="n"/>
       <c r="G302" s="55" t="n"/>
       <c r="H302" s="70" t="n">
-        <v>31.76</v>
+        <v>31.94</v>
       </c>
       <c r="I302" s="71" t="n"/>
     </row>
@@ -18226,7 +18226,7 @@
       <c r="F303" s="59" t="n"/>
       <c r="G303" s="59" t="n"/>
       <c r="H303" s="73" t="n">
-        <v>22.31</v>
+        <v>22.34</v>
       </c>
       <c r="I303" s="74" t="n"/>
     </row>
@@ -18622,7 +18622,7 @@
       </c>
       <c r="B324" s="7" t="inlineStr">
         <is>
-          <t>101 GİRİŞ · BANKO · SİRKÜLASYON — çevre 20,48 m × tavan 2,75 m</t>
+          <t>101 GİRİŞ · BANKO · SİRKÜLASYON — çevre 21,12 m × tavan 2,75 m</t>
         </is>
       </c>
       <c r="C324" s="69" t="inlineStr">
@@ -18634,14 +18634,14 @@
         <v>1</v>
       </c>
       <c r="E324" s="55" t="n">
-        <v>20.48</v>
+        <v>21.12</v>
       </c>
       <c r="F324" s="55" t="n"/>
       <c r="G324" s="55" t="n">
         <v>2.75</v>
       </c>
       <c r="H324" s="70" t="n">
-        <v>56.32</v>
+        <v>58.08</v>
       </c>
       <c r="I324" s="71" t="n"/>
     </row>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="B327" s="48" t="inlineStr">
         <is>
-          <t>102 ARENA · SERBEST AĞIRLIK — çevre 22,59 m × tavan 3,20 m</t>
+          <t>102 ARENA · SERBEST AĞIRLIK — çevre 22,62 m × tavan 3,20 m</t>
         </is>
       </c>
       <c r="C327" s="72" t="inlineStr">
@@ -18721,14 +18721,14 @@
         <v>1</v>
       </c>
       <c r="E327" s="59" t="n">
-        <v>22.59</v>
+        <v>22.62</v>
       </c>
       <c r="F327" s="59" t="n"/>
       <c r="G327" s="59" t="n">
         <v>3.2</v>
       </c>
       <c r="H327" s="73" t="n">
-        <v>72.288</v>
+        <v>72.384</v>
       </c>
       <c r="I327" s="74" t="n"/>
     </row>
@@ -18738,7 +18738,7 @@
       </c>
       <c r="B328" s="7" t="inlineStr">
         <is>
-          <t>103 FONKSİYONEL · KARDİYO — çevre 30,63 m × tavan 3,20 m</t>
+          <t>103 FONKSİYONEL · KARDİYO — çevre 45,39 m × tavan 3,20 m</t>
         </is>
       </c>
       <c r="C328" s="69" t="inlineStr">
@@ -18750,14 +18750,14 @@
         <v>1</v>
       </c>
       <c r="E328" s="55" t="n">
-        <v>30.63</v>
+        <v>45.39</v>
       </c>
       <c r="F328" s="55" t="n"/>
       <c r="G328" s="55" t="n">
         <v>3.2</v>
       </c>
       <c r="H328" s="70" t="n">
-        <v>98.01600000000001</v>
+        <v>145.248</v>
       </c>
       <c r="I328" s="71" t="n"/>
     </row>
@@ -18767,7 +18767,7 @@
       </c>
       <c r="B329" s="48" t="inlineStr">
         <is>
-          <t>104 DİNLENME SALONU — çevre 18,07 m × tavan 2,75 m</t>
+          <t>104 DİNLENME SALONU — çevre 18,17 m × tavan 2,75 m</t>
         </is>
       </c>
       <c r="C329" s="72" t="inlineStr">
@@ -18779,14 +18779,14 @@
         <v>1</v>
       </c>
       <c r="E329" s="59" t="n">
-        <v>18.07</v>
+        <v>18.17</v>
       </c>
       <c r="F329" s="59" t="n"/>
       <c r="G329" s="59" t="n">
         <v>2.75</v>
       </c>
       <c r="H329" s="73" t="n">
-        <v>49.693</v>
+        <v>49.968</v>
       </c>
       <c r="I329" s="74" t="n"/>
     </row>
@@ -18796,7 +18796,7 @@
       </c>
       <c r="B330" s="7" t="inlineStr">
         <is>
-          <t>105 ERKEK SOYUNMA — çevre 8,47 m × tavan 2,60 m</t>
+          <t>105 ERKEK SOYUNMA — çevre 8,52 m × tavan 2,60 m</t>
         </is>
       </c>
       <c r="C330" s="69" t="inlineStr">
@@ -18808,14 +18808,14 @@
         <v>1</v>
       </c>
       <c r="E330" s="55" t="n">
-        <v>8.470000000000001</v>
+        <v>8.52</v>
       </c>
       <c r="F330" s="55" t="n"/>
       <c r="G330" s="55" t="n">
         <v>2.6</v>
       </c>
       <c r="H330" s="70" t="n">
-        <v>22.022</v>
+        <v>22.152</v>
       </c>
       <c r="I330" s="71" t="n"/>
     </row>
@@ -18854,7 +18854,7 @@
       </c>
       <c r="B332" s="7" t="inlineStr">
         <is>
-          <t>108 KADIN SOYUNMA — çevre 9,5 m × tavan 2,60 m</t>
+          <t>108 KADIN SOYUNMA — çevre 9,8 m × tavan 2,60 m</t>
         </is>
       </c>
       <c r="C332" s="69" t="inlineStr">
@@ -18866,14 +18866,14 @@
         <v>1</v>
       </c>
       <c r="E332" s="55" t="n">
-        <v>9.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F332" s="55" t="n"/>
       <c r="G332" s="55" t="n">
         <v>2.6</v>
       </c>
       <c r="H332" s="70" t="n">
-        <v>24.7</v>
+        <v>25.48</v>
       </c>
       <c r="I332" s="71" t="n"/>
     </row>
@@ -19082,7 +19082,7 @@
       </c>
       <c r="B342" s="7" t="inlineStr">
         <is>
-          <t>Erkek WC — çevre 5.4 m × (2,40 − 1,60) m</t>
+          <t>Erkek WC — çevre 5.24 m × (2,40 − 1,60) m</t>
         </is>
       </c>
       <c r="C342" s="69" t="inlineStr">
@@ -19094,14 +19094,14 @@
         <v>1</v>
       </c>
       <c r="E342" s="55" t="n">
-        <v>5.4</v>
+        <v>5.24</v>
       </c>
       <c r="F342" s="55" t="n"/>
       <c r="G342" s="55" t="n">
         <v>0.8</v>
       </c>
       <c r="H342" s="70" t="n">
-        <v>4.32</v>
+        <v>4.192</v>
       </c>
       <c r="I342" s="71" t="n"/>
     </row>
@@ -19111,7 +19111,7 @@
       </c>
       <c r="B343" s="48" t="inlineStr">
         <is>
-          <t>Kadin WC — çevre 5.04 m × (2,40 − 1,60) m</t>
+          <t>Kadin WC — çevre 4.87 m × (2,40 − 1,60) m</t>
         </is>
       </c>
       <c r="C343" s="72" t="inlineStr">
@@ -19123,14 +19123,14 @@
         <v>1</v>
       </c>
       <c r="E343" s="59" t="n">
-        <v>5.04</v>
+        <v>4.87</v>
       </c>
       <c r="F343" s="59" t="n"/>
       <c r="G343" s="59" t="n">
         <v>0.8</v>
       </c>
       <c r="H343" s="73" t="n">
-        <v>4.032</v>
+        <v>3.896</v>
       </c>
       <c r="I343" s="74" t="n"/>
     </row>
@@ -19267,7 +19267,7 @@
       <c r="F350" s="55" t="n"/>
       <c r="G350" s="55" t="n"/>
       <c r="H350" s="70" t="n">
-        <v>15.65</v>
+        <v>15.44</v>
       </c>
       <c r="I350" s="71" t="n"/>
     </row>
@@ -19317,7 +19317,7 @@
       <c r="F352" s="55" t="n"/>
       <c r="G352" s="55" t="n"/>
       <c r="H352" s="70" t="n">
-        <v>4.48</v>
+        <v>4.53</v>
       </c>
       <c r="I352" s="71" t="n"/>
     </row>
@@ -19342,7 +19342,7 @@
       <c r="F353" s="59" t="n"/>
       <c r="G353" s="59" t="n"/>
       <c r="H353" s="73" t="n">
-        <v>5.59</v>
+        <v>5.68</v>
       </c>
       <c r="I353" s="74" t="n"/>
     </row>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="B374" s="7" t="inlineStr">
         <is>
-          <t>Paslanmaz kol, silindirli kilit, 3 adet menteşe · Alt kısmında 150 cm² net hava geçiş menfezi</t>
+          <t>Paslanmaz kol, silindirli kilit, 3 adet menteşe · Alt menfez 150 cm² · SALONA açılır — soyunmada üç kapı açılımı çakışıyordu; kaçış kapısı değildir</t>
         </is>
       </c>
       <c r="C374" s="69" t="inlineStr">
@@ -19875,7 +19875,7 @@
       </c>
       <c r="B381" s="7" t="inlineStr">
         <is>
-          <t>Paslanmaz kol, silindirli kilit, 3 adet menteşe · Alt kısmında 150 cm² net hava geçiş menfezi</t>
+          <t>Paslanmaz kol, silindirli kilit, 3 adet menteşe · Alt menfez 150 cm² · SALONA açılır — soyunmada üç kapı açılımı çakışıyordu; kaçış kapısı değildir</t>
         </is>
       </c>
       <c r="C381" s="69" t="inlineStr">

--- a/output/paket/04_BÜTÇE VE HAKEDİŞ/17Eylül2026_Gym_Maltepe_Kesif_Ozeti_BoQ.xlsx
+++ b/output/paket/04_BÜTÇE VE HAKEDİŞ/17Eylül2026_Gym_Maltepe_Kesif_Ozeti_BoQ.xlsx
@@ -1629,10 +1629,10 @@
         <v/>
       </c>
       <c r="E15" s="17" t="n">
-        <v>539693</v>
+        <v>537495</v>
       </c>
       <c r="F15" s="17" t="n">
-        <v>907712</v>
+        <v>904040</v>
       </c>
       <c r="G15" s="18" t="n">
         <v>0.2</v>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="D17" s="49" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>Z-02</t>
         </is>
       </c>
       <c r="E17" s="50" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="D18" s="41" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>Z-03</t>
         </is>
       </c>
       <c r="E18" s="42" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="D19" s="49" t="inlineStr">
         <is>
-          <t>101 · 104</t>
+          <t>Z-01 · Z-04</t>
         </is>
       </c>
       <c r="E19" s="50" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="D20" s="41" t="inlineStr">
         <is>
-          <t>105 · 108</t>
+          <t>Z-05 · Z-08</t>
         </is>
       </c>
       <c r="E20" s="42" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="D23" s="49" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>Z-02</t>
         </is>
       </c>
       <c r="E23" s="50" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="D24" s="41" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>Z-03</t>
         </is>
       </c>
       <c r="E24" s="42" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="D25" s="49" t="inlineStr">
         <is>
-          <t>101 · 104</t>
+          <t>Z-01 · Z-04</t>
         </is>
       </c>
       <c r="E25" s="50" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="D26" s="41" t="inlineStr">
         <is>
-          <t>106 · 107 · 109 · 110</t>
+          <t>Z-06 · Z-07 · Z-09 · Z-10</t>
         </is>
       </c>
       <c r="E26" s="42" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="D27" s="49" t="inlineStr">
         <is>
-          <t>105 · 108</t>
+          <t>Z-05 · Z-08</t>
         </is>
       </c>
       <c r="E27" s="50" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="D28" s="41" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>Z-02</t>
         </is>
       </c>
       <c r="E28" s="42" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="D29" s="49" t="inlineStr">
         <is>
-          <t>102 · 103</t>
+          <t>Z-02 · Z-03</t>
         </is>
       </c>
       <c r="E29" s="50" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="D30" s="41" t="inlineStr">
         <is>
-          <t>101 · 104</t>
+          <t>Z-01 · Z-04</t>
         </is>
       </c>
       <c r="E30" s="42" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="D31" s="49" t="inlineStr">
         <is>
-          <t>105 · 108</t>
+          <t>Z-05 · Z-08</t>
         </is>
       </c>
       <c r="E31" s="50" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="D39" s="49" t="inlineStr">
         <is>
-          <t>101 · 104</t>
+          <t>Z-01 · Z-04</t>
         </is>
       </c>
       <c r="E39" s="50" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="D40" s="41" t="inlineStr">
         <is>
-          <t>105 · 108</t>
+          <t>Z-05 · Z-08</t>
         </is>
       </c>
       <c r="E40" s="42" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="D41" s="49" t="inlineStr">
         <is>
-          <t>106 · 107 · 109 · 110</t>
+          <t>Z-06 · Z-07 · Z-09 · Z-10</t>
         </is>
       </c>
       <c r="E41" s="50" t="inlineStr">
@@ -4275,7 +4275,7 @@
       </c>
       <c r="D44" s="41" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>Z-02</t>
         </is>
       </c>
       <c r="E44" s="42" t="inlineStr">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="D58" s="41" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>Z-02</t>
         </is>
       </c>
       <c r="E58" s="42" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="D60" s="41" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>Z-01</t>
         </is>
       </c>
       <c r="E60" s="42" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="D62" s="41" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>Z-01</t>
         </is>
       </c>
       <c r="E62" s="42" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="D66" s="41" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>Z-01</t>
         </is>
       </c>
       <c r="E66" s="42" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="D69" s="49" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>Z-01</t>
         </is>
       </c>
       <c r="E69" s="50" t="inlineStr">
@@ -9502,7 +9502,7 @@
         </is>
       </c>
       <c r="D11" s="59" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="E11" s="44" t="n"/>
       <c r="F11" s="54">
@@ -9510,10 +9510,10 @@
         <v/>
       </c>
       <c r="G11" s="60" t="n">
-        <v>1050</v>
+        <v>1260</v>
       </c>
       <c r="H11" s="60" t="n">
-        <v>1800</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
@@ -9533,7 +9533,7 @@
         </is>
       </c>
       <c r="D12" s="55" t="n">
-        <v>16.7</v>
+        <v>13.9</v>
       </c>
       <c r="E12" s="44" t="n"/>
       <c r="F12" s="46">
@@ -9541,10 +9541,10 @@
         <v/>
       </c>
       <c r="G12" s="56" t="n">
-        <v>9018</v>
+        <v>7506</v>
       </c>
       <c r="H12" s="56" t="n">
-        <v>15030</v>
+        <v>12510</v>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
@@ -9781,7 +9781,7 @@
         </is>
       </c>
       <c r="D20" s="55" t="n">
-        <v>44.1</v>
+        <v>41.3</v>
       </c>
       <c r="E20" s="44" t="n"/>
       <c r="F20" s="46">
@@ -9789,10 +9789,10 @@
         <v/>
       </c>
       <c r="G20" s="56" t="n">
-        <v>14112</v>
+        <v>13216</v>
       </c>
       <c r="H20" s="56" t="n">
-        <v>23814</v>
+        <v>22302</v>
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>101 GİRİŞ · BANKO · SİRKÜLASYON</t>
+          <t>Z-01 GİRİŞ · BANKO · SİRKÜLASYON</t>
         </is>
       </c>
       <c r="C7" s="69" t="inlineStr">
@@ -11858,7 +11858,7 @@
       </c>
       <c r="B8" s="48" t="inlineStr">
         <is>
-          <t>102 ARENA · SERBEST AĞIRLIK</t>
+          <t>Z-02 ARENA · SERBEST AĞIRLIK</t>
         </is>
       </c>
       <c r="C8" s="72" t="inlineStr">
@@ -11883,7 +11883,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>103 FONKSİYONEL · KARDİYO</t>
+          <t>Z-03 FONKSİYONEL · KARDİYO</t>
         </is>
       </c>
       <c r="C9" s="69" t="inlineStr">
@@ -11908,7 +11908,7 @@
       </c>
       <c r="B10" s="48" t="inlineStr">
         <is>
-          <t>104 DİNLENME SALONU</t>
+          <t>Z-04 DİNLENME SALONU</t>
         </is>
       </c>
       <c r="C10" s="72" t="inlineStr">
@@ -11933,7 +11933,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>105 ERKEK SOYUNMA</t>
+          <t>Z-05 ERKEK SOYUNMA</t>
         </is>
       </c>
       <c r="C11" s="69" t="inlineStr">
@@ -11958,7 +11958,7 @@
       </c>
       <c r="B12" s="48" t="inlineStr">
         <is>
-          <t>106 ERKEK DUŞ</t>
+          <t>Z-06 ERKEK DUŞ</t>
         </is>
       </c>
       <c r="C12" s="72" t="inlineStr">
@@ -11983,7 +11983,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>107 ERKEK WC</t>
+          <t>Z-07 ERKEK WC</t>
         </is>
       </c>
       <c r="C13" s="69" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="B14" s="48" t="inlineStr">
         <is>
-          <t>108 KADIN SOYUNMA</t>
+          <t>Z-08 KADIN SOYUNMA</t>
         </is>
       </c>
       <c r="C14" s="72" t="inlineStr">
@@ -12033,7 +12033,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>109 KADIN DUŞ</t>
+          <t>Z-09 KADIN DUŞ</t>
         </is>
       </c>
       <c r="C15" s="69" t="inlineStr">
@@ -12058,7 +12058,7 @@
       </c>
       <c r="B16" s="48" t="inlineStr">
         <is>
-          <t>110 KADIN WC</t>
+          <t>Z-10 KADIN WC</t>
         </is>
       </c>
       <c r="C16" s="72" t="inlineStr">
@@ -12220,7 +12220,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>101 GİRİŞ · BANKO · SİRKÜLASYON</t>
+          <t>Z-01 GİRİŞ · BANKO · SİRKÜLASYON</t>
         </is>
       </c>
       <c r="C24" s="69" t="inlineStr">
@@ -12245,7 +12245,7 @@
       </c>
       <c r="B25" s="48" t="inlineStr">
         <is>
-          <t>102 ARENA · SERBEST AĞIRLIK</t>
+          <t>Z-02 ARENA · SERBEST AĞIRLIK</t>
         </is>
       </c>
       <c r="C25" s="72" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>103 FONKSİYONEL · KARDİYO</t>
+          <t>Z-03 FONKSİYONEL · KARDİYO</t>
         </is>
       </c>
       <c r="C26" s="69" t="inlineStr">
@@ -12295,7 +12295,7 @@
       </c>
       <c r="B27" s="48" t="inlineStr">
         <is>
-          <t>104 DİNLENME SALONU</t>
+          <t>Z-04 DİNLENME SALONU</t>
         </is>
       </c>
       <c r="C27" s="72" t="inlineStr">
@@ -12320,7 +12320,7 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>105 ERKEK SOYUNMA</t>
+          <t>Z-05 ERKEK SOYUNMA</t>
         </is>
       </c>
       <c r="C28" s="69" t="inlineStr">
@@ -12345,7 +12345,7 @@
       </c>
       <c r="B29" s="48" t="inlineStr">
         <is>
-          <t>106 ERKEK DUŞ</t>
+          <t>Z-06 ERKEK DUŞ</t>
         </is>
       </c>
       <c r="C29" s="72" t="inlineStr">
@@ -12370,7 +12370,7 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>107 ERKEK WC</t>
+          <t>Z-07 ERKEK WC</t>
         </is>
       </c>
       <c r="C30" s="69" t="inlineStr">
@@ -12395,7 +12395,7 @@
       </c>
       <c r="B31" s="48" t="inlineStr">
         <is>
-          <t>108 KADIN SOYUNMA</t>
+          <t>Z-08 KADIN SOYUNMA</t>
         </is>
       </c>
       <c r="C31" s="72" t="inlineStr">
@@ -12420,7 +12420,7 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>109 KADIN DUŞ</t>
+          <t>Z-09 KADIN DUŞ</t>
         </is>
       </c>
       <c r="C32" s="69" t="inlineStr">
@@ -12445,7 +12445,7 @@
       </c>
       <c r="B33" s="48" t="inlineStr">
         <is>
-          <t>110 KADIN WC</t>
+          <t>Z-10 KADIN WC</t>
         </is>
       </c>
       <c r="C33" s="72" t="inlineStr">
@@ -12607,7 +12607,7 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>106 ERKEK DUŞ</t>
+          <t>Z-06 ERKEK DUŞ</t>
         </is>
       </c>
       <c r="C41" s="69" t="inlineStr">
@@ -12632,7 +12632,7 @@
       </c>
       <c r="B42" s="48" t="inlineStr">
         <is>
-          <t>107 ERKEK WC</t>
+          <t>Z-07 ERKEK WC</t>
         </is>
       </c>
       <c r="C42" s="72" t="inlineStr">
@@ -12657,7 +12657,7 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>109 KADIN DUŞ</t>
+          <t>Z-09 KADIN DUŞ</t>
         </is>
       </c>
       <c r="C43" s="69" t="inlineStr">
@@ -12682,7 +12682,7 @@
       </c>
       <c r="B44" s="48" t="inlineStr">
         <is>
-          <t>110 KADIN WC</t>
+          <t>Z-10 KADIN WC</t>
         </is>
       </c>
       <c r="C44" s="72" t="inlineStr">
@@ -14013,7 +14013,7 @@
       </c>
       <c r="B106" s="66" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>Z-02</t>
         </is>
       </c>
       <c r="F106" s="65" t="inlineStr">
@@ -14090,7 +14090,7 @@
       </c>
       <c r="B108" s="7" t="inlineStr">
         <is>
-          <t>102 ARENA · SERBEST AĞIRLIK</t>
+          <t>Z-02 ARENA · SERBEST AĞIRLIK</t>
         </is>
       </c>
       <c r="C108" s="69" t="inlineStr">
@@ -14150,7 +14150,7 @@
       </c>
       <c r="B113" s="66" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>Z-03</t>
         </is>
       </c>
       <c r="F113" s="65" t="inlineStr">
@@ -14227,7 +14227,7 @@
       </c>
       <c r="B115" s="7" t="inlineStr">
         <is>
-          <t>103 FONKSİYONEL · KARDİYO</t>
+          <t>Z-03 FONKSİYONEL · KARDİYO</t>
         </is>
       </c>
       <c r="C115" s="69" t="inlineStr">
@@ -14287,7 +14287,7 @@
       </c>
       <c r="B120" s="66" t="inlineStr">
         <is>
-          <t>101 · 104</t>
+          <t>Z-01 · Z-04</t>
         </is>
       </c>
       <c r="F120" s="65" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="B122" s="7" t="inlineStr">
         <is>
-          <t>101 GİRİŞ · BANKO · SİRKÜLASYON</t>
+          <t>Z-01 GİRİŞ · BANKO · SİRKÜLASYON</t>
         </is>
       </c>
       <c r="C122" s="69" t="inlineStr">
@@ -14389,7 +14389,7 @@
       </c>
       <c r="B123" s="48" t="inlineStr">
         <is>
-          <t>104 DİNLENME SALONU</t>
+          <t>Z-04 DİNLENME SALONU</t>
         </is>
       </c>
       <c r="C123" s="72" t="inlineStr">
@@ -14449,7 +14449,7 @@
       </c>
       <c r="B128" s="66" t="inlineStr">
         <is>
-          <t>105 · 108</t>
+          <t>Z-05 · Z-08</t>
         </is>
       </c>
       <c r="F128" s="65" t="inlineStr">
@@ -14526,7 +14526,7 @@
       </c>
       <c r="B130" s="7" t="inlineStr">
         <is>
-          <t>105 ERKEK SOYUNMA</t>
+          <t>Z-05 ERKEK SOYUNMA</t>
         </is>
       </c>
       <c r="C130" s="69" t="inlineStr">
@@ -14551,7 +14551,7 @@
       </c>
       <c r="B131" s="48" t="inlineStr">
         <is>
-          <t>108 KADIN SOYUNMA</t>
+          <t>Z-08 KADIN SOYUNMA</t>
         </is>
       </c>
       <c r="C131" s="72" t="inlineStr">
@@ -14688,7 +14688,7 @@
       </c>
       <c r="B138" s="7" t="inlineStr">
         <is>
-          <t>106 ERKEK DUŞ</t>
+          <t>Z-06 ERKEK DUŞ</t>
         </is>
       </c>
       <c r="C138" s="69" t="inlineStr">
@@ -14713,7 +14713,7 @@
       </c>
       <c r="B139" s="48" t="inlineStr">
         <is>
-          <t>107 ERKEK WC</t>
+          <t>Z-07 ERKEK WC</t>
         </is>
       </c>
       <c r="C139" s="72" t="inlineStr">
@@ -14738,7 +14738,7 @@
       </c>
       <c r="B140" s="7" t="inlineStr">
         <is>
-          <t>109 KADIN DUŞ</t>
+          <t>Z-09 KADIN DUŞ</t>
         </is>
       </c>
       <c r="C140" s="69" t="inlineStr">
@@ -14763,7 +14763,7 @@
       </c>
       <c r="B141" s="48" t="inlineStr">
         <is>
-          <t>110 KADIN WC</t>
+          <t>Z-10 KADIN WC</t>
         </is>
       </c>
       <c r="C141" s="72" t="inlineStr">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="B146" s="66" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>Z-02</t>
         </is>
       </c>
       <c r="F146" s="65" t="inlineStr">
@@ -14900,7 +14900,7 @@
       </c>
       <c r="B148" s="7" t="inlineStr">
         <is>
-          <t>102 ARENA · SERBEST AĞIRLIK</t>
+          <t>Z-02 ARENA · SERBEST AĞIRLIK</t>
         </is>
       </c>
       <c r="C148" s="69" t="inlineStr">
@@ -14960,7 +14960,7 @@
       </c>
       <c r="B153" s="66" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>Z-03</t>
         </is>
       </c>
       <c r="F153" s="65" t="inlineStr">
@@ -15037,7 +15037,7 @@
       </c>
       <c r="B155" s="7" t="inlineStr">
         <is>
-          <t>103 FONKSİYONEL · KARDİYO</t>
+          <t>Z-03 FONKSİYONEL · KARDİYO</t>
         </is>
       </c>
       <c r="C155" s="69" t="inlineStr">
@@ -15097,7 +15097,7 @@
       </c>
       <c r="B160" s="66" t="inlineStr">
         <is>
-          <t>101 · 104</t>
+          <t>Z-01 · Z-04</t>
         </is>
       </c>
       <c r="F160" s="65" t="inlineStr">
@@ -15174,7 +15174,7 @@
       </c>
       <c r="B162" s="7" t="inlineStr">
         <is>
-          <t>101 GİRİŞ · BANKO · SİRKÜLASYON</t>
+          <t>Z-01 GİRİŞ · BANKO · SİRKÜLASYON</t>
         </is>
       </c>
       <c r="C162" s="69" t="inlineStr">
@@ -15199,7 +15199,7 @@
       </c>
       <c r="B163" s="48" t="inlineStr">
         <is>
-          <t>104 DİNLENME SALONU</t>
+          <t>Z-04 DİNLENME SALONU</t>
         </is>
       </c>
       <c r="C163" s="72" t="inlineStr">
@@ -15259,7 +15259,7 @@
       </c>
       <c r="B168" s="66" t="inlineStr">
         <is>
-          <t>106 · 107 · 109 · 110</t>
+          <t>Z-06 · Z-07 · Z-09 · Z-10</t>
         </is>
       </c>
       <c r="F168" s="65" t="inlineStr">
@@ -15336,7 +15336,7 @@
       </c>
       <c r="B170" s="7" t="inlineStr">
         <is>
-          <t>106 ERKEK DUŞ</t>
+          <t>Z-06 ERKEK DUŞ</t>
         </is>
       </c>
       <c r="C170" s="69" t="inlineStr">
@@ -15361,7 +15361,7 @@
       </c>
       <c r="B171" s="48" t="inlineStr">
         <is>
-          <t>107 ERKEK WC</t>
+          <t>Z-07 ERKEK WC</t>
         </is>
       </c>
       <c r="C171" s="72" t="inlineStr">
@@ -15386,7 +15386,7 @@
       </c>
       <c r="B172" s="7" t="inlineStr">
         <is>
-          <t>109 KADIN DUŞ</t>
+          <t>Z-09 KADIN DUŞ</t>
         </is>
       </c>
       <c r="C172" s="69" t="inlineStr">
@@ -15411,7 +15411,7 @@
       </c>
       <c r="B173" s="48" t="inlineStr">
         <is>
-          <t>110 KADIN WC</t>
+          <t>Z-10 KADIN WC</t>
         </is>
       </c>
       <c r="C173" s="72" t="inlineStr">
@@ -15471,7 +15471,7 @@
       </c>
       <c r="B178" s="66" t="inlineStr">
         <is>
-          <t>105 · 108</t>
+          <t>Z-05 · Z-08</t>
         </is>
       </c>
       <c r="F178" s="65" t="inlineStr">
@@ -15548,7 +15548,7 @@
       </c>
       <c r="B180" s="7" t="inlineStr">
         <is>
-          <t>105 ERKEK SOYUNMA</t>
+          <t>Z-05 ERKEK SOYUNMA</t>
         </is>
       </c>
       <c r="C180" s="69" t="inlineStr">
@@ -15573,7 +15573,7 @@
       </c>
       <c r="B181" s="48" t="inlineStr">
         <is>
-          <t>108 KADIN SOYUNMA</t>
+          <t>Z-08 KADIN SOYUNMA</t>
         </is>
       </c>
       <c r="C181" s="72" t="inlineStr">
@@ -15633,7 +15633,7 @@
       </c>
       <c r="B186" s="66" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>Z-02</t>
         </is>
       </c>
       <c r="F186" s="65" t="inlineStr">
@@ -15770,7 +15770,7 @@
       </c>
       <c r="B193" s="66" t="inlineStr">
         <is>
-          <t>102 · 103</t>
+          <t>Z-02 · Z-03</t>
         </is>
       </c>
       <c r="F193" s="65" t="inlineStr">
@@ -15847,7 +15847,7 @@
       </c>
       <c r="B195" s="7" t="inlineStr">
         <is>
-          <t>102 ARENA · SERBEST AĞIRLIK — mahal çevresi</t>
+          <t>Z-02 ARENA · SERBEST AĞIRLIK — mahal çevresi</t>
         </is>
       </c>
       <c r="C195" s="69" t="inlineStr">
@@ -15874,7 +15874,7 @@
       </c>
       <c r="B196" s="48" t="inlineStr">
         <is>
-          <t>103 FONKSİYONEL · KARDİYO — mahal çevresi</t>
+          <t>Z-03 FONKSİYONEL · KARDİYO — mahal çevresi</t>
         </is>
       </c>
       <c r="C196" s="72" t="inlineStr">
@@ -15963,7 +15963,7 @@
       </c>
       <c r="B202" s="66" t="inlineStr">
         <is>
-          <t>101 · 104</t>
+          <t>Z-01 · Z-04</t>
         </is>
       </c>
       <c r="F202" s="65" t="inlineStr">
@@ -16040,7 +16040,7 @@
       </c>
       <c r="B204" s="7" t="inlineStr">
         <is>
-          <t>101 GİRİŞ · BANKO · SİRKÜLASYON — mahal çevresi</t>
+          <t>Z-01 GİRİŞ · BANKO · SİRKÜLASYON — mahal çevresi</t>
         </is>
       </c>
       <c r="C204" s="69" t="inlineStr">
@@ -16121,7 +16121,7 @@
       </c>
       <c r="B207" s="48" t="inlineStr">
         <is>
-          <t>104 DİNLENME SALONU — mahal çevresi</t>
+          <t>Z-04 DİNLENME SALONU — mahal çevresi</t>
         </is>
       </c>
       <c r="C207" s="72" t="inlineStr">
@@ -16210,7 +16210,7 @@
       </c>
       <c r="B213" s="66" t="inlineStr">
         <is>
-          <t>105 · 108</t>
+          <t>Z-05 · Z-08</t>
         </is>
       </c>
       <c r="F213" s="65" t="inlineStr">
@@ -16287,7 +16287,7 @@
       </c>
       <c r="B215" s="7" t="inlineStr">
         <is>
-          <t>105 ERKEK SOYUNMA — mahal çevresi</t>
+          <t>Z-05 ERKEK SOYUNMA — mahal çevresi</t>
         </is>
       </c>
       <c r="C215" s="69" t="inlineStr">
@@ -16341,7 +16341,7 @@
       </c>
       <c r="B217" s="7" t="inlineStr">
         <is>
-          <t>108 KADIN SOYUNMA — mahal çevresi</t>
+          <t>Z-08 KADIN SOYUNMA — mahal çevresi</t>
         </is>
       </c>
       <c r="C217" s="69" t="inlineStr">
@@ -16963,7 +16963,7 @@
       </c>
       <c r="B245" s="7" t="inlineStr">
         <is>
-          <t>106 ERKEK DUŞ zemin</t>
+          <t>Z-06 ERKEK DUŞ zemin</t>
         </is>
       </c>
       <c r="C245" s="69" t="inlineStr">
@@ -16988,7 +16988,7 @@
       </c>
       <c r="B246" s="48" t="inlineStr">
         <is>
-          <t>107 ERKEK WC zemin</t>
+          <t>Z-07 ERKEK WC zemin</t>
         </is>
       </c>
       <c r="C246" s="72" t="inlineStr">
@@ -17013,7 +17013,7 @@
       </c>
       <c r="B247" s="7" t="inlineStr">
         <is>
-          <t>109 KADIN DUŞ zemin</t>
+          <t>Z-09 KADIN DUŞ zemin</t>
         </is>
       </c>
       <c r="C247" s="69" t="inlineStr">
@@ -17038,7 +17038,7 @@
       </c>
       <c r="B248" s="48" t="inlineStr">
         <is>
-          <t>110 KADIN WC zemin</t>
+          <t>Z-10 KADIN WC zemin</t>
         </is>
       </c>
       <c r="C248" s="72" t="inlineStr">
@@ -17573,7 +17573,7 @@
       </c>
       <c r="B274" s="66" t="inlineStr">
         <is>
-          <t>101 · 104</t>
+          <t>Z-01 · Z-04</t>
         </is>
       </c>
       <c r="F274" s="65" t="inlineStr">
@@ -17650,7 +17650,7 @@
       </c>
       <c r="B276" s="7" t="inlineStr">
         <is>
-          <t>101 GİRİŞ · BANKO · SİRKÜLASYON</t>
+          <t>Z-01 GİRİŞ · BANKO · SİRKÜLASYON</t>
         </is>
       </c>
       <c r="C276" s="69" t="inlineStr">
@@ -17675,7 +17675,7 @@
       </c>
       <c r="B277" s="48" t="inlineStr">
         <is>
-          <t>104 DİNLENME SALONU</t>
+          <t>Z-04 DİNLENME SALONU</t>
         </is>
       </c>
       <c r="C277" s="72" t="inlineStr">
@@ -17735,7 +17735,7 @@
       </c>
       <c r="B282" s="66" t="inlineStr">
         <is>
-          <t>105 · 108</t>
+          <t>Z-05 · Z-08</t>
         </is>
       </c>
       <c r="F282" s="65" t="inlineStr">
@@ -17812,7 +17812,7 @@
       </c>
       <c r="B284" s="7" t="inlineStr">
         <is>
-          <t>105 ERKEK SOYUNMA</t>
+          <t>Z-05 ERKEK SOYUNMA</t>
         </is>
       </c>
       <c r="C284" s="69" t="inlineStr">
@@ -17837,7 +17837,7 @@
       </c>
       <c r="B285" s="48" t="inlineStr">
         <is>
-          <t>108 KADIN SOYUNMA</t>
+          <t>Z-08 KADIN SOYUNMA</t>
         </is>
       </c>
       <c r="C285" s="72" t="inlineStr">
@@ -17897,7 +17897,7 @@
       </c>
       <c r="B290" s="66" t="inlineStr">
         <is>
-          <t>106 · 107 · 109 · 110</t>
+          <t>Z-06 · Z-07 · Z-09 · Z-10</t>
         </is>
       </c>
       <c r="F290" s="65" t="inlineStr">
@@ -17974,7 +17974,7 @@
       </c>
       <c r="B292" s="7" t="inlineStr">
         <is>
-          <t>106 ERKEK DUŞ</t>
+          <t>Z-06 ERKEK DUŞ</t>
         </is>
       </c>
       <c r="C292" s="69" t="inlineStr">
@@ -17999,7 +17999,7 @@
       </c>
       <c r="B293" s="48" t="inlineStr">
         <is>
-          <t>107 ERKEK WC</t>
+          <t>Z-07 ERKEK WC</t>
         </is>
       </c>
       <c r="C293" s="72" t="inlineStr">
@@ -18024,7 +18024,7 @@
       </c>
       <c r="B294" s="7" t="inlineStr">
         <is>
-          <t>109 KADIN DUŞ</t>
+          <t>Z-09 KADIN DUŞ</t>
         </is>
       </c>
       <c r="C294" s="69" t="inlineStr">
@@ -18049,7 +18049,7 @@
       </c>
       <c r="B295" s="48" t="inlineStr">
         <is>
-          <t>110 KADIN WC</t>
+          <t>Z-10 KADIN WC</t>
         </is>
       </c>
       <c r="C295" s="72" t="inlineStr">
@@ -18186,7 +18186,7 @@
       </c>
       <c r="B302" s="7" t="inlineStr">
         <is>
-          <t>102 ARENA · SERBEST AĞIRLIK</t>
+          <t>Z-02 ARENA · SERBEST AĞIRLIK</t>
         </is>
       </c>
       <c r="C302" s="69" t="inlineStr">
@@ -18211,7 +18211,7 @@
       </c>
       <c r="B303" s="48" t="inlineStr">
         <is>
-          <t>103 FONKSİYONEL · KARDİYO</t>
+          <t>Z-03 FONKSİYONEL · KARDİYO</t>
         </is>
       </c>
       <c r="C303" s="72" t="inlineStr">
@@ -18408,7 +18408,7 @@
       </c>
       <c r="B315" s="66" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>Z-02</t>
         </is>
       </c>
       <c r="F315" s="65" t="inlineStr">
@@ -18622,7 +18622,7 @@
       </c>
       <c r="B324" s="7" t="inlineStr">
         <is>
-          <t>101 GİRİŞ · BANKO · SİRKÜLASYON — çevre 21,12 m × tavan 2,75 m</t>
+          <t>Z-01 GİRİŞ · BANKO · SİRKÜLASYON — çevre 21,12 m × tavan 2,75 m</t>
         </is>
       </c>
       <c r="C324" s="69" t="inlineStr">
@@ -18709,7 +18709,7 @@
       </c>
       <c r="B327" s="48" t="inlineStr">
         <is>
-          <t>102 ARENA · SERBEST AĞIRLIK — çevre 22,62 m × tavan 3,20 m</t>
+          <t>Z-02 ARENA · SERBEST AĞIRLIK — çevre 22,62 m × tavan 3,20 m</t>
         </is>
       </c>
       <c r="C327" s="72" t="inlineStr">
@@ -18738,7 +18738,7 @@
       </c>
       <c r="B328" s="7" t="inlineStr">
         <is>
-          <t>103 FONKSİYONEL · KARDİYO — çevre 45,39 m × tavan 3,20 m</t>
+          <t>Z-03 FONKSİYONEL · KARDİYO — çevre 45,39 m × tavan 3,20 m</t>
         </is>
       </c>
       <c r="C328" s="69" t="inlineStr">
@@ -18767,7 +18767,7 @@
       </c>
       <c r="B329" s="48" t="inlineStr">
         <is>
-          <t>104 DİNLENME SALONU — çevre 18,17 m × tavan 2,75 m</t>
+          <t>Z-04 DİNLENME SALONU — çevre 18,17 m × tavan 2,75 m</t>
         </is>
       </c>
       <c r="C329" s="72" t="inlineStr">
@@ -18796,7 +18796,7 @@
       </c>
       <c r="B330" s="7" t="inlineStr">
         <is>
-          <t>105 ERKEK SOYUNMA — çevre 8,52 m × tavan 2,60 m</t>
+          <t>Z-05 ERKEK SOYUNMA — çevre 8,52 m × tavan 2,60 m</t>
         </is>
       </c>
       <c r="C330" s="69" t="inlineStr">
@@ -18854,7 +18854,7 @@
       </c>
       <c r="B332" s="7" t="inlineStr">
         <is>
-          <t>108 KADIN SOYUNMA — çevre 9,8 m × tavan 2,60 m</t>
+          <t>Z-08 KADIN SOYUNMA — çevre 9,8 m × tavan 2,60 m</t>
         </is>
       </c>
       <c r="C332" s="69" t="inlineStr">
@@ -19252,7 +19252,7 @@
       </c>
       <c r="B350" s="7" t="inlineStr">
         <is>
-          <t>101 GİRİŞ · BANKO · SİRKÜLASYON</t>
+          <t>Z-01 GİRİŞ · BANKO · SİRKÜLASYON</t>
         </is>
       </c>
       <c r="C350" s="69" t="inlineStr">
@@ -19277,7 +19277,7 @@
       </c>
       <c r="B351" s="48" t="inlineStr">
         <is>
-          <t>104 DİNLENME SALONU</t>
+          <t>Z-04 DİNLENME SALONU</t>
         </is>
       </c>
       <c r="C351" s="72" t="inlineStr">
@@ -19302,7 +19302,7 @@
       </c>
       <c r="B352" s="7" t="inlineStr">
         <is>
-          <t>105 ERKEK SOYUNMA</t>
+          <t>Z-05 ERKEK SOYUNMA</t>
         </is>
       </c>
       <c r="C352" s="69" t="inlineStr">
@@ -19327,7 +19327,7 @@
       </c>
       <c r="B353" s="48" t="inlineStr">
         <is>
-          <t>108 KADIN SOYUNMA</t>
+          <t>Z-08 KADIN SOYUNMA</t>
         </is>
       </c>
       <c r="C353" s="72" t="inlineStr">
@@ -20620,7 +20620,7 @@
       </c>
       <c r="B421" s="66" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>Z-02</t>
         </is>
       </c>
       <c r="F421" s="65" t="inlineStr">
@@ -20898,7 +20898,7 @@
       </c>
       <c r="B435" s="66" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>Z-01</t>
         </is>
       </c>
       <c r="F435" s="65" t="inlineStr">
@@ -21097,7 +21097,7 @@
       </c>
       <c r="B444" s="66" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>Z-01</t>
         </is>
       </c>
       <c r="F444" s="65" t="inlineStr">
@@ -21645,7 +21645,7 @@
       </c>
       <c r="B472" s="66" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>Z-01</t>
         </is>
       </c>
       <c r="F472" s="65" t="inlineStr">
@@ -21919,7 +21919,7 @@
       </c>
       <c r="B486" s="66" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>Z-01</t>
         </is>
       </c>
       <c r="F486" s="65" t="inlineStr">
